--- a/data/output/clean_statement.xlsx
+++ b/data/output/clean_statement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Transactions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -82,7 +79,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -90,33 +87,27 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -573,11 +564,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'AUTOMOBILE' indicating auto parts shop</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -615,11 +606,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'AUTOMOBILE' indicating auto parts shop, but incomplete</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -657,11 +648,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HPCENTRE' indicating HP petrol pump</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -699,11 +690,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -741,11 +732,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -774,7 +765,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SALARY SALMARSIZWAN</t>
+          <t>SALARY CREDIT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -787,7 +778,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Exact match with payroll category definition</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -825,11 +816,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -867,11 +858,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'MOTORS' indicating vehicle servicing</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -909,11 +900,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -951,11 +942,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HPCL' indicating fuel purchase, but incomplete</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -993,11 +984,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -1026,7 +1017,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SALARY SALAPR SIZWAN</t>
+          <t>SALARY SIZWAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1039,7 +1030,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Exact match with payroll category definition</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -1077,11 +1068,11 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -1119,11 +1110,11 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
         </is>
       </c>
       <c r="G15" t="b">
@@ -1161,11 +1152,11 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G16" t="b">
@@ -1203,11 +1194,11 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description is too garbled to classify</t>
         </is>
       </c>
       <c r="G17" s="3" t="b">
@@ -1245,11 +1236,11 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description is too generic to classify</t>
         </is>
       </c>
       <c r="G18" s="3" t="b">
@@ -1287,11 +1278,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
         </is>
       </c>
       <c r="G19" t="b">
@@ -1329,11 +1320,11 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G20" t="b">
@@ -1371,11 +1362,11 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G21" t="b">
@@ -1413,11 +1404,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G22" t="b">
@@ -1455,11 +1446,11 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description is too generic to classify</t>
         </is>
       </c>
       <c r="G23" s="3" t="b">
@@ -1497,11 +1488,11 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'FUELCENTRE' indicating fuel centre</t>
         </is>
       </c>
       <c r="G24" t="b">
@@ -1539,11 +1530,11 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
         </is>
       </c>
       <c r="G25" t="b">
@@ -1581,11 +1572,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
         </is>
       </c>
       <c r="G26" t="b">
@@ -1623,11 +1614,11 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HPCL' indicating fuel purchase, but incomplete</t>
         </is>
       </c>
       <c r="G27" t="b">
@@ -1665,11 +1656,11 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G28" t="b">
@@ -1707,11 +1698,11 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description is too generic to classify</t>
         </is>
       </c>
       <c r="G29" s="3" t="b">
@@ -1749,11 +1740,11 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
         </is>
       </c>
       <c r="G30" t="b">
@@ -1791,11 +1782,11 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'AUTOMOBILE' indicating auto parts shop</t>
         </is>
       </c>
       <c r="G31" t="b">
@@ -1833,11 +1824,11 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'AUTOMOBILE' indicating auto parts shop, but incomplete</t>
         </is>
       </c>
       <c r="G32" t="b">
@@ -1866,7 +1857,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SALARY SALMAY SIZWAN</t>
+          <t>SALARY SIZWAN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1879,7 +1870,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Exact match with payroll category definition</t>
         </is>
       </c>
       <c r="G33" t="b">
@@ -1917,11 +1908,11 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G34" t="b">
@@ -1959,11 +1950,11 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G35" t="b">
@@ -2001,11 +1992,11 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HPCENTRE' indicating HP petrol pump</t>
         </is>
       </c>
       <c r="G36" t="b">
@@ -2043,11 +2034,11 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G37" t="b">
@@ -2085,11 +2076,11 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'FUE' indicating fuel purchase, but incomplete</t>
         </is>
       </c>
       <c r="G38" t="b">
@@ -2127,11 +2118,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
         </is>
       </c>
       <c r="G39" t="b">
@@ -2169,11 +2160,11 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HPCL' indicating fuel purchase, but incomplete</t>
         </is>
       </c>
       <c r="G40" t="b">
@@ -2211,11 +2202,11 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
         </is>
       </c>
       <c r="G41" t="b">
@@ -2253,11 +2244,11 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G42" t="b">
@@ -2295,11 +2286,11 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
         </is>
       </c>
       <c r="G43" t="b">
@@ -2316,44 +2307,44 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>01/07/2018</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>CREDITINTERESTCAPITALISED</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>CREDITINTERESTCAPITALISED</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Migrated from legacy flat cache.</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="2" t="n">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Credit Card Repayment</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>80</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Description contains 'CREDITINTEREST' indicating credit card repayment</t>
+        </is>
+      </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
         <v>29</v>
       </c>
-      <c r="J44" s="2" t="n">
+      <c r="J44" t="n">
         <v>74.90000000000001</v>
       </c>
     </row>
@@ -2370,7 +2361,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SALARY SALJUN SIZWAN</t>
+          <t>SALARY SIZWAN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2383,7 +2374,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Exact match with payroll category definition</t>
         </is>
       </c>
       <c r="G45" t="b">
@@ -2421,11 +2412,11 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G46" t="b">
@@ -2463,11 +2454,11 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
         </is>
       </c>
       <c r="G47" t="b">
@@ -2509,7 +2500,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Cash withdrawn from ATM in East Delhi</t>
         </is>
       </c>
       <c r="G48" t="b">
@@ -2551,7 +2542,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Cash withdrawn from ATM in East Delhi</t>
         </is>
       </c>
       <c r="G49" t="b">
@@ -2589,11 +2580,11 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G50" t="b">
@@ -2631,11 +2622,11 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
         </is>
       </c>
       <c r="G51" t="b">
@@ -2677,7 +2668,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Cash withdrawn from ATM in East Delhi</t>
         </is>
       </c>
       <c r="G52" t="b">
@@ -2715,11 +2706,11 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HPCENTRE' indicating HP petrol pump</t>
         </is>
       </c>
       <c r="G53" t="b">
@@ -2757,11 +2748,11 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
         </is>
       </c>
       <c r="G54" t="b">
@@ -2799,11 +2790,11 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HPCL' indicating fuel purchase, but incomplete</t>
         </is>
       </c>
       <c r="G55" t="b">
@@ -2832,7 +2823,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SALARY SALJULY SIZWAN</t>
+          <t>SALARY SIZWAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2845,7 +2836,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Exact match with payroll category definition</t>
         </is>
       </c>
       <c r="G56" t="b">
@@ -2883,11 +2874,11 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G57" t="b">
@@ -2929,7 +2920,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G58" t="b">
@@ -2971,7 +2962,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Cash withdrawn from ATM in Bulandshahar</t>
         </is>
       </c>
       <c r="G59" t="b">
@@ -3009,11 +3000,11 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
         </is>
       </c>
       <c r="G60" t="b">
@@ -3055,7 +3046,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G61" t="b">
@@ -3097,7 +3088,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G62" t="b">
@@ -3135,11 +3126,11 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Unknown description, possibly a person's name</t>
         </is>
       </c>
       <c r="G63" s="3" t="b">
@@ -3181,7 +3172,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G64" t="b">
@@ -3223,7 +3214,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G65" t="b">
@@ -3265,7 +3256,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G66" t="b">
@@ -3294,7 +3285,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SALARY SALAUG SIZWAN</t>
+          <t>SALARY SIZWAN</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3307,7 +3298,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Exact match with payroll category definition</t>
         </is>
       </c>
       <c r="G67" t="b">
@@ -3345,11 +3336,11 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
         </is>
       </c>
       <c r="G68" t="b">
@@ -3387,11 +3378,11 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G69" t="b">
@@ -3433,7 +3424,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Internal transfer between own accounts</t>
         </is>
       </c>
       <c r="G70" t="b">
@@ -3475,7 +3466,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Cash withdrawn from ATM in Kaimur</t>
         </is>
       </c>
       <c r="G71" t="b">
@@ -3513,11 +3504,11 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Payment for online shopping on Amazon</t>
         </is>
       </c>
       <c r="G72" t="b">
@@ -3546,7 +3537,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ONE97COMMUNICATPO</t>
+          <t>PAYTMPO</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3555,11 +3546,11 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Paytm is a popular e-commerce and retail payment platform</t>
         </is>
       </c>
       <c r="G73" t="b">
@@ -3597,11 +3588,11 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G74" t="b">
@@ -3643,7 +3634,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Purchase from medical supplier UKAR HEALTHCARE</t>
         </is>
       </c>
       <c r="G75" t="b">
@@ -3681,11 +3672,11 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Payment for mobile recharge on Airtel</t>
         </is>
       </c>
       <c r="G76" t="b">
@@ -3702,44 +3693,44 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>01/10/2018</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>CREDITINTERESTCAPITALISED</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>CREDITINTERESTCAPITALISED</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>Migrated from legacy flat cache.</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="2" t="n">
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Credit Card Repayment</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>80</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Description contains 'CREDITINTEREST' indicating credit card repayment</t>
+        </is>
+      </c>
+      <c r="G77" t="b">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
         <v>21</v>
       </c>
-      <c r="J77" s="2" t="n">
+      <c r="J77" t="n">
         <v>1981.7</v>
       </c>
     </row>
@@ -3765,11 +3756,11 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Unknown description, possibly a person's name</t>
         </is>
       </c>
       <c r="G78" s="3" t="b">
@@ -3807,11 +3798,11 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G79" t="b">
@@ -3849,11 +3840,11 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G80" t="b">
@@ -3895,7 +3886,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G81" t="b">
@@ -3937,7 +3928,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G82" t="b">
@@ -3979,7 +3970,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Purchase from medical supplier UKAR HEALTHCARE</t>
         </is>
       </c>
       <c r="G83" t="b">
@@ -4021,7 +4012,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G84" t="b">
@@ -4063,7 +4054,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G85" t="b">
@@ -4105,7 +4096,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G86" t="b">
@@ -4147,7 +4138,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G87" t="b">
@@ -4176,7 +4167,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SALARY SALSEP SIZWAN</t>
+          <t>SALARY SIZWAN</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4189,7 +4180,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Exact match with payroll category definition</t>
         </is>
       </c>
       <c r="G88" t="b">
@@ -4231,7 +4222,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Internal transfer between own accounts</t>
         </is>
       </c>
       <c r="G89" t="b">
@@ -4273,7 +4264,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Internal transfer between own accounts</t>
         </is>
       </c>
       <c r="G90" t="b">
@@ -4311,11 +4302,11 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G91" t="b">
@@ -4353,11 +4344,11 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Generic UPI transfer to unknown merchant</t>
         </is>
       </c>
       <c r="G92" t="b">
@@ -4395,11 +4386,11 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>ATM usage fee of Rs. 388</t>
         </is>
       </c>
       <c r="G93" t="b">
@@ -4437,11 +4428,11 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G94" t="b">
@@ -4479,11 +4470,11 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>ATM usage fee of Rs. 670</t>
         </is>
       </c>
       <c r="G95" t="b">
@@ -4521,11 +4512,11 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Non-cash ATM usage fee</t>
         </is>
       </c>
       <c r="G96" t="b">
@@ -4563,11 +4554,11 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Generic UPI transfer to unknown merchant</t>
         </is>
       </c>
       <c r="G97" t="b">
@@ -4605,11 +4596,11 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Generic UPI transfer to unknown merchant</t>
         </is>
       </c>
       <c r="G98" t="b">
@@ -4638,7 +4629,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SALARY SALOCT SIZWAN</t>
+          <t>SALARY SIZWAN</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4651,7 +4642,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Exact match with payroll category definition</t>
         </is>
       </c>
       <c r="G99" t="b">
@@ -4680,7 +4671,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>TPS*PHONEPERECHPO</t>
+          <t>PHONEPERECHPO</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4689,11 +4680,11 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>PhonePe is a mobile recharge and utility payment service</t>
         </is>
       </c>
       <c r="G100" t="b">
@@ -4731,11 +4722,11 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Online shopping transaction from BestDeal</t>
         </is>
       </c>
       <c r="G101" t="b">
@@ -4777,7 +4768,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Purchase from medical supplier UKAR HEALTHCARE</t>
         </is>
       </c>
       <c r="G102" t="b">
@@ -4815,11 +4806,11 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Generic UPI transfer to unknown merchant</t>
         </is>
       </c>
       <c r="G103" t="b">
@@ -4861,7 +4852,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G104" t="b">
@@ -4903,7 +4894,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Purchase from medical supplier UKAR HEALTHCARE</t>
         </is>
       </c>
       <c r="G105" t="b">
@@ -4945,7 +4936,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G106" t="b">
@@ -4983,11 +4974,11 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Generic UPI transfer to unknown merchant</t>
         </is>
       </c>
       <c r="G107" t="b">
@@ -5025,11 +5016,11 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Generic UPI transfer to unknown merchant</t>
         </is>
       </c>
       <c r="G108" t="b">
@@ -5067,11 +5058,11 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Generic UPI transfer to unknown merchant</t>
         </is>
       </c>
       <c r="G109" t="b">
@@ -5109,11 +5100,11 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Generic UPI transfer to unknown merchant</t>
         </is>
       </c>
       <c r="G110" t="b">
@@ -5151,11 +5142,11 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Generic UPI transfer to unknown merchant</t>
         </is>
       </c>
       <c r="G111" t="b">
@@ -5193,11 +5184,11 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Generic UPI transfer to unknown merchant</t>
         </is>
       </c>
       <c r="G112" t="b">
@@ -5235,11 +5226,11 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Generic UPI transfer to unknown merchant</t>
         </is>
       </c>
       <c r="G113" t="b">
@@ -5281,7 +5272,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G114" t="b">
@@ -5323,7 +5314,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G115" t="b">
@@ -5365,7 +5356,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G116" t="b">
@@ -5407,7 +5398,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G117" t="b">
@@ -5449,7 +5440,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G118" t="b">
@@ -5491,7 +5482,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G119" t="b">
@@ -5529,11 +5520,11 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Generic UPI transfer to unknown merchant</t>
         </is>
       </c>
       <c r="G120" t="b">
@@ -5575,7 +5566,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G121" t="b">
@@ -5617,7 +5608,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G122" t="b">
@@ -5659,7 +5650,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G123" t="b">
@@ -5701,7 +5692,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G124" t="b">
@@ -5730,7 +5721,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SALARY SALNOV SIZWAN</t>
+          <t>SALARY SIZWAN</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5743,7 +5734,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Exact match with payroll category definition</t>
         </is>
       </c>
       <c r="G125" t="b">
@@ -5781,11 +5772,11 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G126" t="b">
@@ -5823,11 +5814,11 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Cash deposited into the account on 10 DEC 18</t>
         </is>
       </c>
       <c r="G127" t="b">
@@ -5869,7 +5860,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Internal transfer between own accounts</t>
         </is>
       </c>
       <c r="G128" t="b">
@@ -5886,44 +5877,44 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="A129" t="inlineStr">
         <is>
           <t>01/01/2019</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>CREDITINTERESTCAPITALISED</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>CREDITINTERESTCAPITALISED</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>Migrated from legacy flat cache.</t>
-        </is>
-      </c>
-      <c r="G129" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" s="2" t="n">
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Credit Card Repayment</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>80</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Description contains 'CREDITINTEREST' indicating credit card repayment</t>
+        </is>
+      </c>
+      <c r="G129" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
         <v>13</v>
       </c>
-      <c r="J129" s="2" t="n">
+      <c r="J129" t="n">
         <v>15.83</v>
       </c>
     </row>
@@ -5949,11 +5940,11 @@
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Unknown description, possibly a person's name</t>
         </is>
       </c>
       <c r="G130" s="3" t="b">
@@ -5991,11 +5982,11 @@
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Unknown description, possibly a person's name</t>
         </is>
       </c>
       <c r="G131" s="3" t="b">
@@ -6037,7 +6028,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G132" t="b">
@@ -6079,7 +6070,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G133" t="b">
@@ -6121,7 +6112,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G134" t="b">
@@ -6163,7 +6154,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G135" t="b">
@@ -6205,7 +6196,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G136" t="b">
@@ -6247,7 +6238,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G137" t="b">
@@ -6289,7 +6280,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G138" t="b">
@@ -6331,7 +6322,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G139" t="b">
@@ -6369,11 +6360,11 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Cash deposited into the account on 08 JAN 19</t>
         </is>
       </c>
       <c r="G140" t="b">
@@ -6402,7 +6393,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SALARY SALDEC SIZWAN</t>
+          <t>SALARY SIZWAN</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6415,7 +6406,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Exact match with payroll category definition</t>
         </is>
       </c>
       <c r="G141" t="b">
@@ -6457,7 +6448,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Internal transfer between own accounts</t>
         </is>
       </c>
       <c r="G142" t="b">
@@ -6495,11 +6486,11 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Advance salary payment to employees</t>
         </is>
       </c>
       <c r="G143" t="b">
@@ -6537,11 +6528,11 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G144" t="b">
@@ -6579,11 +6570,11 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>ATM usage fee charged by the bank</t>
         </is>
       </c>
       <c r="G145" t="b">
@@ -6621,11 +6612,11 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Cash withdrawn from ATM in West Delhi</t>
         </is>
       </c>
       <c r="G146" t="b">
@@ -6663,11 +6654,11 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Cash withdrawn from ATM in West Delhi</t>
         </is>
       </c>
       <c r="G147" t="b">
@@ -6705,11 +6696,11 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Generic UPI transfer to unknown merchant</t>
         </is>
       </c>
       <c r="G148" t="b">
@@ -6747,11 +6738,11 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>IRCTC train ticket booking transaction</t>
         </is>
       </c>
       <c r="G149" t="b">
@@ -6789,11 +6780,11 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G150" t="b">
@@ -6831,11 +6822,11 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Train ticket booking transaction from KGN Railwax</t>
         </is>
       </c>
       <c r="G151" t="b">
@@ -6873,11 +6864,11 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Train ticket booking transaction from KGN Railwax</t>
         </is>
       </c>
       <c r="G152" t="b">
@@ -6915,11 +6906,11 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G153" t="b">
@@ -6957,11 +6948,11 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Train ticket booking transaction from KGN Railwax</t>
         </is>
       </c>
       <c r="G154" t="b">
@@ -7003,7 +6994,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G155" t="b">
@@ -7045,7 +7036,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G156" t="b">
@@ -7087,7 +7078,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G157" t="b">
@@ -7129,7 +7120,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G158" t="b">
@@ -7171,7 +7162,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G159" t="b">
@@ -7209,11 +7200,11 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Generic UPI transfer to unknown merchant</t>
         </is>
       </c>
       <c r="G160" t="b">
@@ -7251,11 +7242,11 @@
         </is>
       </c>
       <c r="E161" s="2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Unknown transaction</t>
         </is>
       </c>
       <c r="G161" s="3" t="b">
@@ -7293,11 +7284,11 @@
         </is>
       </c>
       <c r="E162" s="2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Unknown transaction</t>
         </is>
       </c>
       <c r="G162" s="3" t="b">
@@ -7335,11 +7326,11 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
         </is>
       </c>
       <c r="G163" t="b">
@@ -7377,11 +7368,11 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Generic UPI transfer to unknown merchant</t>
         </is>
       </c>
       <c r="G164" t="b">
@@ -7419,11 +7410,11 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Generic UPI transfer to unknown merchant</t>
         </is>
       </c>
       <c r="G165" t="b">
@@ -7465,7 +7456,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G166" t="b">
@@ -7507,7 +7498,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G167" t="b">
@@ -7545,11 +7536,11 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Cash deposited into the account on 06 MAR 19</t>
         </is>
       </c>
       <c r="G168" t="b">
@@ -7591,7 +7582,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G169" t="b">
@@ -7633,7 +7624,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G170" t="b">
@@ -7671,11 +7662,11 @@
         </is>
       </c>
       <c r="E171" s="2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Unknown transaction</t>
         </is>
       </c>
       <c r="G171" s="3" t="b">
@@ -7713,11 +7704,11 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Cash deposited into the account on 18 MAR 19</t>
         </is>
       </c>
       <c r="G172" t="b">
@@ -7759,7 +7750,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Migrated from legacy flat cache.</t>
+          <t>Cash withdrawn from ATM in East Delhi</t>
         </is>
       </c>
       <c r="G173" t="b">
@@ -7776,44 +7767,44 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+      <c r="A174" t="inlineStr">
         <is>
           <t>01/04/2019</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>CREDITINTERESTCAPITALISED</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>CREDITINTERESTCAPITALISED</t>
         </is>
       </c>
-      <c r="D174" s="2" t="inlineStr">
-        <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="E174" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F174" s="2" t="inlineStr">
-        <is>
-          <t>Migrated from legacy flat cache.</t>
-        </is>
-      </c>
-      <c r="G174" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H174" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I174" s="2" t="n">
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Credit Card Repayment</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>80</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Description contains 'CREDITINTEREST' indicating credit card repayment</t>
+        </is>
+      </c>
+      <c r="G174" t="b">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+      <c r="I174" t="n">
         <v>16</v>
       </c>
-      <c r="J174" s="2" t="n">
+      <c r="J174" t="n">
         <v>23.05</v>
       </c>
     </row>
@@ -7940,7 +7931,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -7998,16 +7989,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C11" t="n">
         <v>98071</v>
       </c>
       <c r="D11" t="n">
-        <v>78053</v>
+        <v>78132</v>
       </c>
       <c r="E11" t="n">
-        <v>-20018</v>
+        <v>-19939</v>
       </c>
     </row>
     <row r="12">
@@ -8150,16 +8141,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
         <v>611</v>
       </c>
       <c r="D19" t="n">
-        <v>55062</v>
+        <v>54983</v>
       </c>
       <c r="E19" t="n">
-        <v>54451</v>
+        <v>54372</v>
       </c>
     </row>
     <row r="20">

--- a/data/output/clean_statement.xlsx
+++ b/data/output/clean_statement.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -79,7 +82,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -87,27 +90,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -475,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J174"/>
+  <dimension ref="A1:J139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -545,22 +554,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>02/04/2018</t>
+          <t>03/04/2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608MASIHAUTOMOBILEPO POS DEBIT</t>
+          <t>NEFT-HDFC0000234-TECHPARK ESTATES LLP OFFICE RENT APR-2023</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MASIHAUTOMOBILEPO</t>
+          <t>NEFT HDFC0000234 TECHPARK ESTATES LLP OFFICE RENT APR 2023</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fuel &amp; Auto</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -568,83 +577,83 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Description contains 'AUTOMOBILE' indicating auto parts shop</t>
+          <t>Rent payment to Techpark Estates LLP indicates a utility expense.</t>
         </is>
       </c>
       <c r="G2" t="b">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>130</v>
+        <v>185000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>5411.09</v>
+        <v>1657350</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>04/04/2018</t>
+          <t>05/04/2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>POSREF541919******3608-04/04MASIHAUT</t>
+          <t>RTGS-ICIC0000567-CLOUDINFRA SERVICES AWS/GCP VENDOR BILL APR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MASIHAUT</t>
+          <t>RTGS ICIC0000567 CLOUDINFRA SERVICES AWS GCP VENDOR BILL APR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fuel &amp; Auto</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Description contains 'AUTOMOBILE' indicating auto parts shop, but incomplete</t>
+          <t>AWS and GCP vendor bill indicates a software and IT expense.</t>
         </is>
       </c>
       <c r="G3" t="b">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>320000</v>
       </c>
       <c r="I3" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>5412.07</v>
+        <v>1337350</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>05/04/2018</t>
+          <t>07/04/2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608HPCENTREMOTINPO POS DEBIT</t>
+          <t>BULK NEFT-SALARY APR-2023 PRANAV MEHTA Rs.95K | SNEHA IYER Rs.88K ROHAN DESAI Rs.72K | ANANYA SINGH Rs.68.5K</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HPCENTREMOTINPO</t>
+          <t>BULK NEFT SALARY APR 2023 PRANAV MEHTA Rs 95K | SNEHA IYER Rs 88K ROHAN DESAI Rs 72K | ANANYA SINGH Rs 68 5K</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fuel &amp; Auto</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -652,41 +661,41 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Description contains 'HPCENTRE' indicating HP petrol pump</t>
+          <t>Bulk NEFT salary payment indicates payroll credits to employees.</t>
         </is>
       </c>
       <c r="G4" t="b">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>130</v>
+        <v>323500</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>5282.07</v>
+        <v>1013850</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>05/04/2018</t>
+          <t>10/04/2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCARE.PO POS DEBIT</t>
+          <t>RTGS-HDFC0004365-NEXGEN SOFTWARE LLP CLIENT PROJECT ADVANCE RECD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UKARHEALTHCARE PO</t>
+          <t>RTGS HDFC0004365 NEXGEN SOFTWARE LLP CLIENT PROJECT ADVANCE RECD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -694,125 +703,125 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
+          <t>Nexgen Software LLP indicates a software and IT expense.</t>
         </is>
       </c>
       <c r="G5" t="b">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1250000</v>
       </c>
       <c r="J5" t="n">
-        <v>4782.07</v>
+        <v>2263850</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/04/2018</t>
+          <t>12/04/2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ATW-541919XXXXXX3608-S1AWDE11-DELHI</t>
+          <t>NEFT-ICIC0009876-DIGITAL SPARK MEDIA MARKETING CAMPAIGN APR Q1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL DELHI</t>
+          <t>NEFT ICIC0009876 DIGITAL SPARK MEDIA MARKETING CAMPAIGN APR Q1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>Digital Spark Media marketing campaign may involve e-commerce or retail expenses.</t>
         </is>
       </c>
       <c r="G6" t="b">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4500</v>
+        <v>45000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>282.07</v>
+        <v>2218850</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/04/2018</t>
+          <t>14/04/2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UKARHEALTHCAR-SALMARSIZWAN</t>
+          <t>IMPS-230414009-MAKEMYTRIP BIZ FLIGHT BLR-HYD TEAM OFFSITE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SALARY CREDIT</t>
+          <t>MAKEMYTRIP BIZ FLIGHT BLR HYD TEAM OFFSITE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Travel &amp; Transport</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Exact match with payroll category definition</t>
+          <t>MakeMyTrip business flight booking indicates travel and transport expenses.</t>
         </is>
       </c>
       <c r="G7" t="b">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>28600</v>
       </c>
       <c r="I7" t="n">
-        <v>13887</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>14169.07</v>
+        <v>2190250</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/04/2018</t>
+          <t>17/04/2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCARE.PO POS DEBIT</t>
+          <t>NEFT-HDFC0005678-SOFTLICENCE HUB MICROSOFT 365 ANNUAL RENEWAL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UKARHEALTHCARE PO</t>
+          <t>NEFT HDFC0005678 SOFTLICENCE HUB MICROSOFT 365 ANNUAL RENEWAL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -820,217 +829,217 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
+          <t>Microsoft 365 annual renewal indicates a software and IT expense.</t>
         </is>
       </c>
       <c r="G8" t="b">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>150</v>
+        <v>110000</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>14019.07</v>
+        <v>2080250</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/04/2018</t>
+          <t>20/04/2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608DEEPAKMOTORSPOSD EBIT</t>
+          <t>NEFT-SBIN0007654-GST PAYMENT APR-23 GSTN: 27AABCA1234B1Z5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DEEPAKMOTORSPOSD</t>
+          <t>NEFT SBIN0007654 GST PAYMENT APR 23 GSTN: 27AABCA1234B1Z5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fuel &amp; Auto</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Description contains 'MOTORS' indicating vehicle servicing</t>
+          <t>GST payment may involve utility or telecom expenses.</t>
         </is>
       </c>
       <c r="G9" t="b">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>210</v>
+        <v>78500</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>13809.07</v>
+        <v>2001750</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/04/2018</t>
+          <t>22/04/2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ATW-541919XXXXXX3608-S1ANDH54-DELHI</t>
+          <t>RTGS-HDFC0008901-INFOSEC SOLUTIONS CYBER SECURITY AUDIT FEES</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL DELHI</t>
+          <t>RTGS HDFC0008901 INFOSEC SOLUTIONS CYBER SECURITY AUDIT FEES</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>Infosec Solutions cyber security audit fees indicate a software and IT expense.</t>
         </is>
       </c>
       <c r="G10" t="b">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>13500</v>
+        <v>75000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>309.07</v>
+        <v>1926750</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/04/2018</t>
+          <t>25/04/2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CRVPOS541919******3608HPCL0.75%CASH</t>
+          <t>CC 000789456XXXXXX2341 AUTOPAY-TAD CORPORATE CARD STMT APR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HPCL0 75%CASH</t>
+          <t>CREDIT CARD AUTOPAY TAD CORPORATE CARD STMT APR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Fuel &amp; Auto</t>
+          <t>Credit Card Repayment</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Description contains 'HPCL' indicating fuel purchase, but incomplete</t>
+          <t>Credit card autopay indicates credit card repayment.</t>
         </is>
       </c>
       <c r="G11" t="b">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>38200</v>
       </c>
       <c r="I11" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>310.05</v>
+        <v>1888550</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/04/2018</t>
+          <t>28/04/2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCARE.PO POS DEBIT</t>
+          <t>NEFT-AXIS0004567-FINTAX ADVISORY PROFESSIONAL FEES Q1 FY24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UKARHEALTHCARE PO</t>
+          <t>NEFT AXIS0004567 FINTAX ADVISORY PROFESSIONAL FEES Q1 FY24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
+          <t>Fintax Advisory professional fees may involve e-commerce or retail expenses.</t>
         </is>
       </c>
       <c r="G12" t="b">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>300</v>
+        <v>55000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>10.05</v>
+        <v>1833550</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/05/2018</t>
+          <t>30/04/2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UKARHEALTHCAR-SALAPR.SIZWAN</t>
+          <t>CREDIT INTEREST CAPITALISED</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SALARY SIZWAN</t>
+          <t>CREDIT INTEREST CAPITALISED</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Interest &amp; Dividends</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Exact match with payroll category definition</t>
+          <t>Credit interest capitalized indicates interest and dividend income.</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -1040,31 +1049,31 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>13887</v>
+        <v>2840</v>
       </c>
       <c r="J13" t="n">
-        <v>13897.05</v>
+        <v>1836390</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/05/2018</t>
+          <t>03/05/2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCARE.PO POS DEBIT</t>
+          <t>NEFT-HDFC0000234-TECHPARK ESTATES LLP OFFICE RENT MAY-2023 LIMITED</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UKARHEALTHCARE PO</t>
+          <t>NEFT HDFC0000234 TECHPARK ESTATES LLP OFFICE RENT MAY 2023 LIMITED</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1072,41 +1081,41 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
+          <t>Rent payment to Techpark Estates LLP indicates a utility expense.</t>
         </is>
       </c>
       <c r="G14" t="b">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>300</v>
+        <v>185000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>13597.05</v>
+        <v>1651390</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/05/2018</t>
+          <t>05/05/2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCARE.PO POS DEBIT</t>
+          <t>RTGS-ICIC0000567-CLOUDINFRA SERVICES AWS USAGE BILL APR CYCLE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UKARHEALTHCARE PO</t>
+          <t>RTGS ICIC0000567 CLOUDINFRA SERVICES AWS USAGE BILL APR CYCLE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1114,167 +1123,167 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
+          <t>AWS usage bill indicates a software and IT expense.</t>
         </is>
       </c>
       <c r="G15" t="b">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>500</v>
+        <v>287400</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>13097.05</v>
+        <v>1363990</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/05/2018</t>
+          <t>07/05/2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EAW-541919XXXXXX3608-DECN1263-GHAZIABAD</t>
+          <t>BULK NEFT-SALARY MAY-2023 4 EMPLOYEES — SAME STRUCTURE AS APR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL GHAZIABAD</t>
+          <t>BULK NEFT SALARY MAY 2023 4 EMPLOYEES — SAME STRUCTURE AS APR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>Bulk NEFT salary payment indicates payroll credits to employees.</t>
         </is>
       </c>
       <c r="G16" t="b">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>500</v>
+        <v>323500</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>12597.05</v>
+        <v>1040490</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2018</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>2232052,AMAN</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>,AMAN</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Description is too garbled to classify</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>50000</v>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>62597.05</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>10/05/2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>RTGS-HDFC0004365-NEXGEN SOFTWARE LLP PROJECT MILESTONE 1 PAYMENT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>RTGS HDFC0004365 NEXGEN SOFTWARE LLP PROJECT MILESTONE 1 PAYMENT</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Software &amp; IT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>90</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nexgen Software LLP indicates a software and IT expense.</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1875000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2915490</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2018</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>UPI-50100217698175-PRATAP.RAGHAV1990@OKH DFCBANK-PAY-812913381742-UPI</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>DFCBANK</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Description is too generic to classify</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>62596.05</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>12/05/2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NEFT-ICIC0009876-DIGITAL SPARK MEDIA SEO &amp; CONTENT MARKETING MAY</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NEFT ICIC0009876 DIGITAL SPARK MEDIA SEO &amp; CONTENT MARKETING MAY</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>E-Commerce &amp; Retail</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>70</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Digital Spark Media SEO and content marketing may involve e-commerce or retail expenses.</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>45000</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2870490</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/05/2018</t>
+          <t>15/05/2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCARE.PO POS DEBIT</t>
+          <t>IMPS-230515019-OYO BUSINESS ACCOM HYDERABAD OFFSITE 3N/4D</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UKARHEALTHCARE PO</t>
+          <t>OYO BUSINESS ACCOM HYDERABAD OFFSITE 3N 4D</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Travel &amp; Transport</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1282,209 +1291,209 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
+          <t>OYO business accommodation booking indicates travel and transport expenses.</t>
         </is>
       </c>
       <c r="G19" t="b">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2000</v>
+        <v>42000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>60596.05</v>
+        <v>2828490</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/05/2018</t>
+          <t>18/05/2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ATW-541919XXXXXX3608-S1AWDE11-DELHI</t>
+          <t>NEFT-SBIN0007654-ADVANCE TAX Q1 AY 2024-25 CHALLAN NO. 280</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL DELHI</t>
+          <t>NEFT SBIN0007654 ADVANCE TAX Q1 AY 2024 25 CHALLAN NO 280</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>Advance tax payment may involve utility or telecom expenses.</t>
         </is>
       </c>
       <c r="G20" t="b">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>25000</v>
+        <v>108000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>35596.05</v>
+        <v>2720490</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/05/2018</t>
+          <t>20/05/2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ATW-541919XXXXXX3608-S1AWDE11-DELHI</t>
+          <t>NEFT-HDFC0009012-ERGODESK SOLUTIONS OFFICE FURNITURE 12 UNITS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL DELHI</t>
+          <t>NEFT HDFC0009012 ERGODESK SOLUTIONS OFFICE FURNITURE 12 UNITS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>Ergodesk Solutions office furniture purchase may involve e-commerce or retail expenses.</t>
         </is>
       </c>
       <c r="G21" t="b">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>5000</v>
+        <v>96000</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>30596.05</v>
+        <v>2624490</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10/05/2018</t>
+          <t>22/05/2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ATW-541919XXXXXX3608-S1AWDE11-DELHI</t>
+          <t>RTGS-KOTAK0001122-NETPLUS ILINK LEASED LINE RENEWAL 1 YR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL DELHI</t>
+          <t>RTGS KOTAK0001122 NETPLUS ILINK LEASED LINE RENEWAL 1 YR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>Leased line renewal indicates a software or IT service</t>
         </is>
       </c>
       <c r="G22" t="b">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>11000</v>
+        <v>120000</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>19596.05</v>
+        <v>2504490</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2018</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>POS541919XXXXXX3608PTM*PAYTMPOSDEBIT</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>PAYTM</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Description is too generic to classify</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>210</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>19386.05</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>25/05/2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CC 000789456XXXXXX2341 AUTOPAY-TAD CORPORATE CARD STMT MAY</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CREDIT CARD AUTOPAY TAD CORPORATE CARD STMT MAY</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Credit Card Repayment</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Autopay indicates a credit card repayment</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>52750</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2451740</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>12/05/2018</t>
+          <t>31/05/2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608DEEPFUELCENTREPO POS DEBIT</t>
+          <t>CREDIT INTEREST CAPITALISED</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DEEPFUELCENTREPO</t>
+          <t>CREDIT INTEREST CAPITALISED</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Fuel &amp; Auto</t>
+          <t>Interest &amp; Dividends</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1492,167 +1501,167 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Description contains 'FUELCENTRE' indicating fuel centre</t>
+          <t>Credit interest capitalized indicates interest and dividend income.</t>
         </is>
       </c>
       <c r="G24" t="b">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>3610</v>
       </c>
       <c r="J24" t="n">
-        <v>19216.05</v>
+        <v>2455350</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>13/05/2018</t>
+          <t>02/06/2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCARE.PO POS DEBIT</t>
+          <t>NEFT-HDFC0000234-TECHPARK ESTATES LLP OFFICE RENT JUN-2023</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UKARHEALTHCARE PO</t>
+          <t>NEFT HDFC0000234 TECHPARK ESTATES LLP OFFICE RENT JUN 2023</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
+          <t>Office rent likely includes utilities or telecom services</t>
         </is>
       </c>
       <c r="G25" t="b">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>200</v>
+        <v>185000</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>19016.05</v>
+        <v>2270350</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>14/05/2018</t>
+          <t>05/06/2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCARE.PO POS DEBIT</t>
+          <t>RTGS-ICIC0000567-CLOUDINFRA SERVICES AWS USAGE BILL MAY CYCLE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UKARHEALTHCARE PO</t>
+          <t>RTGS ICIC0000567 CLOUDINFRA SERVICES AWS USAGE BILL MAY CYCLE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
+          <t>AWS usage indicates a software or IT service</t>
         </is>
       </c>
       <c r="G26" t="b">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>500</v>
+        <v>311200</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>18516.05</v>
+        <v>1959150</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>15/05/2018</t>
+          <t>07/06/2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CRVPOS541919******3608HPCL0.75%CASH</t>
+          <t>BULK NEFT-SALARY JUN-2023 4 EMPLOYEES PROCESSED LIMITED</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HPCL0 75%CASH</t>
+          <t>BULK NEFT SALARY JUN 2023 4 EMPLOYEES PROCESSED LIMITED</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fuel &amp; Auto</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Description contains 'HPCL' indicating fuel purchase, but incomplete</t>
+          <t>Bulk NEFT indicates a payroll transaction</t>
         </is>
       </c>
       <c r="G27" t="b">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>323500</v>
       </c>
       <c r="I27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>18517.33</v>
+        <v>1635650</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>16/05/2018</t>
+          <t>09/06/2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ATW-541919XXXXXX3608-S1AWDE11-DELHI</t>
+          <t>RTGS-HDFC0004365-NEXGEN SOFTWARE LLP Q1 PROJECT COMPLETION PAYMENT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL DELHI</t>
+          <t>RTGS HDFC0004365 NEXGEN SOFTWARE LLP Q1 PROJECT COMPLETION PAYMENT</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1660,83 +1669,83 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>Software LLP indicates a software or IT service</t>
         </is>
       </c>
       <c r="G28" t="b">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>2200000</v>
       </c>
       <c r="J28" t="n">
-        <v>517.33</v>
+        <v>3835650</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2018</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>POS541919XXXXXX3608PAYTMPOSDEBIT</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>PAYTM</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Description is too generic to classify</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>317.33</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>12/06/2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NEFT-AXIS0007890-LINKEDIN INDIA RECRUITMENT ADS JUN CAMPAIGN</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NEFT AXIS0007890 LINKEDIN INDIA RECRUITMENT ADS JUN CAMPAIGN</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>E-Commerce &amp; Retail</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>80</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Recruitment ads likely include online advertising</t>
+        </is>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>32000</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3803650</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>17/05/2018</t>
+          <t>14/06/2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCARE.PO POS DEBIT</t>
+          <t>IMPS-230614029-CLEARTRIP BIZ FLT MUM-DEL-MUM SALES TEAM</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UKARHEALTHCARE PO</t>
+          <t>CLEARTRIP BIZ FLT MUM DEL MUM SALES TEAM</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Travel &amp; Transport</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1744,125 +1753,125 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
+          <t>Cleartrip indicates a travel or transport service</t>
         </is>
       </c>
       <c r="G30" t="b">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>200</v>
+        <v>18400</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>117.33</v>
+        <v>3785250</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>19/05/2018</t>
+          <t>16/06/2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608MASIHAUTOMOBILEPO POS DEBIT</t>
+          <t>NEFT-SBIN0007654-GST PAYMENT JUN-23 GSTN: 27AABCA1234B1Z5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MASIHAUTOMOBILEPO</t>
+          <t>NEFT SBIN0007654 GST PAYMENT JUN 23 GSTN: 27AABCA1234B1Z5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Fuel &amp; Auto</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Description contains 'AUTOMOBILE' indicating auto parts shop</t>
+          <t>GST payment likely includes utilities or telecom services</t>
         </is>
       </c>
       <c r="G31" t="b">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>95</v>
+        <v>55000</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>22.33</v>
+        <v>3730250</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>21/05/2018</t>
+          <t>19/06/2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>POSREF541919******3608-05/21MASIHAUT</t>
+          <t>NEFT-HDFC0003456-ZENDESK INDIA SUPPORT TOOL ANNUAL LICENSE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MASIHAUT</t>
+          <t>NEFT HDFC0003456 ZENDESK INDIA SUPPORT TOOL ANNUAL LICENSE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fuel &amp; Auto</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Description contains 'AUTOMOBILE' indicating auto parts shop, but incomplete</t>
+          <t>Zendesk indicates a software or IT service</t>
         </is>
       </c>
       <c r="G32" t="b">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>84000</v>
       </c>
       <c r="I32" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>23.04</v>
+        <v>3646250</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>04/06/2018</t>
+          <t>25/06/2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UKARHEALTHCAR-SALMAY.SIZWAN</t>
+          <t>CC 000789456XXXXXX2341 AUTOPAY-TAD CORPORATE CARD STMT JUN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SALARY SIZWAN</t>
+          <t>CREDIT CARD AUTOPAY TAD CORPORATE CARD STMT JUN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Credit Card Repayment</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1870,251 +1879,251 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Exact match with payroll category definition</t>
+          <t>Autopay indicates a credit card repayment</t>
         </is>
       </c>
       <c r="G33" t="b">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>61300</v>
       </c>
       <c r="I33" t="n">
-        <v>18690</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>18713.04</v>
+        <v>3584950</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>04/06/2018</t>
+          <t>28/06/2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NWD-541919XXXXXX3608-00691225-DELHI</t>
+          <t>NEFT-HDFC0001234-ELECBILL MSEDCL ELECTRICITY BILL JUN-2023</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL 00691225 DELHI</t>
+          <t>NEFT HDFC0001234 ELECBILL MSEDCL ELECTRICITY BILL JUN 2023</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>Electricity bill indicates a utility or telecom service</t>
         </is>
       </c>
       <c r="G34" t="b">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>5500</v>
+        <v>22400</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>13213.04</v>
+        <v>3562550</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/06/2018</t>
+          <t>30/06/2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ATW-541919XXXXXX3608-S1AWDE11-DELHI</t>
+          <t>CREDIT INTEREST CAPITALISED LIMITED</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL DELHI</t>
+          <t>CREDIT INTEREST CAPITALISED LIMITED</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Loan &amp; EMI</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>Credit interest capitalized likely includes a loan or EMI</t>
         </is>
       </c>
       <c r="G35" t="b">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>5500</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="J35" t="n">
-        <v>7713.04</v>
+        <v>3567530</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>09/06/2018</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>POS541919XXXXXX3608HPCENTREMOTINPO POS DEBIT</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>HPCENTREMOTINPO</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>03/07/2023</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>NEFT-HDFC0000234-TECHPARK ESTATES LLP OFFICE RENT JUL-2023</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>NEFT HDFC0000234 TECHPARK ESTATES LLP OFFICE RENT JUL 2023</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Fuel &amp; Auto</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v>90</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Description contains 'HPCENTRE' indicating HP petrol pump</t>
-        </is>
-      </c>
-      <c r="G36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>170</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>7543.04</v>
+      <c r="E36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Unable to determine category due to unclear description</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>185000</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>3382530</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/06/2018</t>
+          <t>05/07/2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NWD-541919XXXXXX3608-APN2685A-NEWDELHI</t>
+          <t>RTGS-ICIC0000567-CLOUDINFRA SERVICES AWS USAGE BILL JUN CYCLE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL NEWDELHI</t>
+          <t>RTGS ICIC0000567 CLOUDINFRA SERVICES AWS USAGE BILL JUN CYCLE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>Strong match for Software &amp; IT category due to AWS usage</t>
         </is>
       </c>
       <c r="G37" t="b">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>5000</v>
+        <v>344000</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>2543.04</v>
+        <v>3038530</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12/06/2018</t>
+          <t>07/07/2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CRVPOS541919******3608DISCOUNTONFUE</t>
+          <t>BULK NEFT-SALARY JUL-2023 5 EMPLOYEES (NEW HIRE: VIKRAM RAO Rs.82K)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DISCOUNTONFUE</t>
+          <t>BULK NEFT SALARY JUL 2023 5 EMPLOYEES (NEW HIRE: VIKRAM RAO Rs 82K)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Fuel &amp; Auto</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Description contains 'FUE' indicating fuel purchase, but incomplete</t>
+          <t>Clear match for Payroll category due to salary payment</t>
         </is>
       </c>
       <c r="G38" t="b">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>405500</v>
       </c>
       <c r="I38" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>2544.62</v>
+        <v>2633030</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12/06/2018</t>
+          <t>10/07/2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCARE.PO POS DEBIT</t>
+          <t>RTGS-HDFC0004365-NEXGEN SOFTWARE LLP NEW PROJECT KICKOFF ADVANCE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UKARHEALTHCARE PO</t>
+          <t>RTGS HDFC0004365 NEXGEN SOFTWARE LLP NEW PROJECT KICKOFF ADVANCE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -2122,83 +2131,83 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
+          <t>Strong match for Software &amp; IT category due to software company</t>
         </is>
       </c>
       <c r="G39" t="b">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1400000</v>
       </c>
       <c r="J39" t="n">
-        <v>544.62</v>
+        <v>4033030</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12/06/2018</t>
+          <t>12/07/2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CRVPOS541919******3608HPCL0.75%CASH</t>
+          <t>NEFT-ICIC0009876-DIGITAL SPARK MEDIA GOOGLE ADS MANAGEMENT JUL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HPCL0 75%CASH</t>
+          <t>NEFT ICIC0009876 DIGITAL SPARK MEDIA GOOGLE ADS MANAGEMENT JUL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Fuel &amp; Auto</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Description contains 'HPCL' indicating fuel purchase, but incomplete</t>
+          <t>Probable match for E-Commerce &amp; Retail category due to Google Ads</t>
         </is>
       </c>
       <c r="G40" t="b">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="I40" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>545.9</v>
+        <v>3988030</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>14/06/2018</t>
+          <t>14/07/2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCARE.PO POS DEBIT</t>
+          <t>NEFT-HDFC0005432-AWS INDIA PVT LTD RESERVED INSTANCE PURCHASE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UKARHEALTHCARE PO</t>
+          <t>NEFT HDFC0005432 AWS INDIA PVT LTD RESERVED INSTANCE PURCHASE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -2206,83 +2215,83 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
+          <t>Strong match for Software &amp; IT category due to AWS purchase</t>
         </is>
       </c>
       <c r="G41" t="b">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>200</v>
+        <v>210000</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>345.9</v>
+        <v>3778030</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>18/06/2018</t>
+          <t>18/07/2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NWD-541919XXXXXX3608-N3357300-AJMER</t>
+          <t>NEFT-SBIN0007654-GST PAYMENT JUL-23 GSTN: 27AABCA1234B1Z5</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL AJMER</t>
+          <t>NEFT SBIN0007654 GST PAYMENT JUL 23 GSTN: 27AABCA1234B1Z5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>Probable match for Utilities &amp; Telecom category due to GST payment</t>
         </is>
       </c>
       <c r="G42" t="b">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>200</v>
+        <v>82000</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>145.9</v>
+        <v>3696030</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>21/06/2018</t>
+          <t>20/07/2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCARE.PO POS DEBIT</t>
+          <t>IMPS-230720008-INDIGO AIRLINES BIZ FLT MUM-BLR 4 PAX TECH SUMMIT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UKARHEALTHCARE PO</t>
+          <t>INDIGO AIRLINES BIZ FLT MUM BLR 4 PAX TECH SUMMIT</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Travel &amp; Transport</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -2290,167 +2299,167 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
+          <t>Clear match for Travel &amp; Transport category due to airline booking</t>
         </is>
       </c>
       <c r="G43" t="b">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>100</v>
+        <v>48200</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>45.9</v>
+        <v>3647830</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>01/07/2018</t>
+          <t>22/07/2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CREDITINTERESTCAPITALISED</t>
+          <t>NEFT-HDFC0009876-NASSCOM INDIA ANNUAL MEMBERSHIP FEES FY24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CREDITINTERESTCAPITALISED</t>
+          <t>NEFT HDFC0009876 NASSCOM INDIA ANNUAL MEMBERSHIP FEES FY24</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Description contains 'CREDITINTEREST' indicating credit card repayment</t>
+          <t>Probable match for E-Commerce &amp; Retail category due to membership fees</t>
         </is>
       </c>
       <c r="G44" t="b">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="I44" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>74.90000000000001</v>
+        <v>3572830</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>04/07/2018</t>
+          <t>25/07/2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UKARHEALTHCAR-SALJUN.SIZWAN</t>
+          <t>CC 000789456XXXXXX2341 AUTOPAY-TAD CORPORATE CARD STMT JUL</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SALARY SIZWAN</t>
+          <t>CREDIT CARD AUTOPAY TAD CORPORATE CARD STMT JUL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Credit Card Repayment</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Exact match with payroll category definition</t>
+          <t>Clear match for Credit Card Repayment category due to autopay</t>
         </is>
       </c>
       <c r="G45" t="b">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>68500</v>
       </c>
       <c r="I45" t="n">
-        <v>16690</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>16764.9</v>
+        <v>3504330</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>04/07/2018</t>
+          <t>28/07/2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ATW-541919XXXXXX3608-S1ANDH24-DELHI</t>
+          <t>NEFT-HDFC0001234-ELECBILL MSEDCL ELECTRICITY BILL JUL-2023</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL DELHI</t>
+          <t>NEFT HDFC0001234 ELECBILL MSEDCL ELECTRICITY BILL JUL 2023</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>Clear match for Utilities &amp; Telecom category due to electricity bill</t>
         </is>
       </c>
       <c r="G46" t="b">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>13000</v>
+        <v>24800</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>3764.9</v>
+        <v>3479530</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>05/07/2018</t>
+          <t>31/07/2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCARE.PO POS DEBIT</t>
+          <t>CREDIT INTEREST CAPITALISED</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>UKARHEALTHCARE PO</t>
+          <t>CREDIT INTEREST CAPITALISED</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Interest &amp; Dividends</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -2458,251 +2467,251 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
+          <t>Credit interest capitalized indicates interest and dividend income.</t>
         </is>
       </c>
       <c r="G47" t="b">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>5720</v>
       </c>
       <c r="J47" t="n">
-        <v>3614.9</v>
+        <v>3485250</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>05/07/2018</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>ATW-541919XXXXXX3608-S1AWDE11-EASTDELHI</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>ATM WITHDRAWAL EASTDELHI</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>ATM Withdrawal</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>100</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Cash withdrawn from ATM in East Delhi</t>
-        </is>
-      </c>
-      <c r="G48" t="b">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>500</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>3114.9</v>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>02/08/2023</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>NEFT-HDFC0000234-TECHPARK ESTATES LLP OFFICE RENT AUG-2023 LIMITED</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>NEFT HDFC0000234 TECHPARK ESTATES LLP OFFICE RENT AUG 2023 LIMITED</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Fuel &amp; Auto</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Unable to determine category due to unclear description</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>185000</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>3300250</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/07/2018</t>
+          <t>05/08/2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ATW-541919XXXXXX3608-S1AWDE12-EASTDELHI</t>
+          <t>RTGS-ICIC0000567-CLOUDINFRA SERVICES AWS USAGE BILL JUL CYCLE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL EASTDELHI</t>
+          <t>RTGS ICIC0000567 CLOUDINFRA SERVICES AWS USAGE BILL JUL CYCLE</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cash withdrawn from ATM in East Delhi</t>
+          <t>Strong match for Software &amp; IT category due to AWS usage</t>
         </is>
       </c>
       <c r="G49" t="b">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>500</v>
+        <v>368000</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>2614.9</v>
+        <v>2932250</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>13/07/2018</t>
+          <t>07/08/2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NWD-541919XXXXXX3608-SPCND016-NEWDELHI</t>
+          <t>BULK NEFT-SALARY AUG-2023 5 EMPLOYEES PROCESSED</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL NEWDELHI</t>
+          <t>BULK NEFT SALARY AUG 2023 5 EMPLOYEES PROCESSED</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>Clear match for Payroll category due to salary payment</t>
         </is>
       </c>
       <c r="G50" t="b">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>500</v>
+        <v>405500</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>2114.9</v>
+        <v>2526750</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16/07/2018</t>
+          <t>10/08/2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCARE.PO POS DEBIT</t>
+          <t>RTGS-HDFC0004365-INFOZEAL TECH INC CLIENT PAYMENT RECD USD 45K</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UKARHEALTHCARE PO</t>
+          <t>RTGS HDFC0004365 INFOZEAL TECH INC CLIENT PAYMENT RECD USD 45K</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
+          <t>Probable match for Software &amp; IT category due to software company</t>
         </is>
       </c>
       <c r="G51" t="b">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>3726000</v>
       </c>
       <c r="J51" t="n">
-        <v>1614.9</v>
+        <v>6252750</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>16/07/2018</t>
+          <t>12/08/2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ATW-541919XXXXXX3608-S1AWDE12-EASTDELHI</t>
+          <t>NEFT-ICIC0009876-DIGITAL SPARK MEDIA SEO &amp; SOCIAL MEDIA AUG</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL EASTDELHI</t>
+          <t>NEFT ICIC0009876 DIGITAL SPARK MEDIA SEO &amp; SOCIAL MEDIA AUG</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cash withdrawn from ATM in East Delhi</t>
+          <t>Probable match for E-Commerce &amp; Retail category due to SEO services</t>
         </is>
       </c>
       <c r="G52" t="b">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>500</v>
+        <v>45000</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>1114.9</v>
+        <v>6207750</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>21/07/2018</t>
+          <t>15/08/2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608HPCENTREMOTINPO POS DEBIT</t>
+          <t>NEFT-HDFC0002345-EPISODE SIX TECH SAAS TOOL ANNUAL CONTRACT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HPCENTREMOTINPO</t>
+          <t>NEFT HDFC0002345 EPISODE SIX TECH SAAS TOOL ANNUAL CONTRACT</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Fuel &amp; Auto</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -2710,251 +2719,251 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Description contains 'HPCENTRE' indicating HP petrol pump</t>
+          <t>Strong match for Software &amp; IT category due to SAAS tool</t>
         </is>
       </c>
       <c r="G53" t="b">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>70</v>
+        <v>180000</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>1044.9</v>
+        <v>6027750</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>21/07/2018</t>
+          <t>18/08/2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCARE.PO POS DEBIT</t>
+          <t>NEFT-SBIN0007654-GST PAYMENT AUG-23 GSTN: 27AABCA1234B1Z5</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>UKARHEALTHCARE PO</t>
+          <t>NEFT SBIN0007654 GST PAYMENT AUG 23 GSTN: 27AABCA1234B1Z5</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
+          <t>Probable match for Utilities &amp; Telecom category due to GST payment</t>
         </is>
       </c>
       <c r="G54" t="b">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1000</v>
+        <v>95000</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>44.9</v>
+        <v>5932750</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>24/07/2018</t>
+          <t>20/08/2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CRVPOS541919******3608HPCL0.75%CASH</t>
+          <t>IMPS-230820018-TAJ HOTELS BUSINESS ACCOM PUNE 2N CLIENT MEETING</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HPCL0 75%CASH</t>
+          <t>TAJ HOTELS BUSINESS ACCOM PUNE 2N CLIENT MEETING</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Fuel &amp; Auto</t>
+          <t>Travel &amp; Transport</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Description contains 'HPCL' indicating fuel purchase, but incomplete</t>
+          <t>Clear match for Travel &amp; Transport category due to hotel booking</t>
         </is>
       </c>
       <c r="G55" t="b">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>32400</v>
       </c>
       <c r="I55" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>45.42</v>
+        <v>5900350</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/08/2018</t>
+          <t>22/08/2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>UKARHEALTHCAR-SALJULY.SIZWAN</t>
+          <t>NEFT-AXIS0006789-BRAND ELEVATE CO EXPO BOOTH DESIGN &amp; BRANDING</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SALARY SIZWAN</t>
+          <t>NEFT AXIS0006789 BRAND ELEVATE CO EXPO BOOTH DESIGN &amp; BRANDING</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Exact match with payroll category definition</t>
+          <t>Probable match for E-Commerce &amp; Retail category due to expo booth design</t>
         </is>
       </c>
       <c r="G56" t="b">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="I56" t="n">
-        <v>16690</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>16735.42</v>
+        <v>5780350</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/08/2018</t>
+          <t>25/08/2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NWD-541919XXXXXX3608-SPCND016-NEWDELHI</t>
+          <t>CC 000789456XXXXXX2341 AUTOPAY-TAD CORPORATE CARD STMT AUG</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL NEWDELHI</t>
+          <t>CREDIT CARD AUTOPAY TAD CORPORATE CARD STMT AUG</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Credit Card Repayment</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>Autopay payment towards corporate credit card dues.</t>
         </is>
       </c>
       <c r="G57" t="b">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>4500</v>
+        <v>74200</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>12235.42</v>
+        <v>5706150</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08/08/2018</t>
+          <t>31/08/2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CC000489377XXXXXX6183AUTOPAYSI-TAD</t>
+          <t>CREDIT INTEREST CAPITALISED</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>CREDIT INTEREST CAPITALISED</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Interest &amp; Dividends</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Credit interest capitalized indicates interest and dividend income.</t>
         </is>
       </c>
       <c r="G58" t="b">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>1187</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>8960</v>
       </c>
       <c r="J58" t="n">
-        <v>11048.42</v>
+        <v>5715110</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10/08/2018</t>
+          <t>02/09/2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NWD-541919XXXXXX3608-D3619800-BULANDSHAH R</t>
+          <t>NEFT-HDFC0000234-TECHPARK ESTATES LLP OFFICE RENT SEP-2023</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL BULANDSHAH R</t>
+          <t>NEFT HDFC0000234 TECHPARK ESTATES LLP OFFICE RENT SEP 2023</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Fund Transfer</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -2962,83 +2971,83 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cash withdrawn from ATM in Bulandshahar</t>
+          <t>Office rent payment to Techpark Estates LLP via NEFT.</t>
         </is>
       </c>
       <c r="G59" t="b">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>5000</v>
+        <v>185000</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>6048.42</v>
+        <v>5530110</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>14/08/2018</t>
+          <t>05/09/2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCARE.PO POS DEBIT</t>
+          <t>RTGS-ICIC0000567-CLOUDINFRA SERVICES AWS USAGE BILL AUG CYCLE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>UKARHEALTHCARE PO</t>
+          <t>RTGS ICIC0000567 CLOUDINFRA SERVICES AWS USAGE BILL AUG CYCLE</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
+          <t>AWS usage bill payment to Cloudinfra Services via RTGS.</t>
         </is>
       </c>
       <c r="G60" t="b">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>6045</v>
+        <v>320000</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>3.42</v>
+        <v>5210110</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/09/2018</t>
+          <t>07/09/2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CC000524181XXXXXX7263AUTOPAYSI-MAD</t>
+          <t>BULK NEFT-SALARY SEP-2023 5 EMPLOYEES PROCESSED LIMITED</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>BULK NEFT SALARY SEP 2023 5 EMPLOYEES PROCESSED LIMITED</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -3046,41 +3055,41 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Bulk salary payment to 5 employees via NEFT.</t>
         </is>
       </c>
       <c r="G61" t="b">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1666</v>
+        <v>405500</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>-1662.58</v>
+        <v>4804610</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/09/2018</t>
+          <t>10/09/2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CC000524181XXXXXX7263AUTOPAYSI-MAD</t>
+          <t>RTGS-HDFC0004365-NEXGEN SOFTWARE LLP PROJECT PHASE 2 MILESTONE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>RTGS HDFC0004365 NEXGEN SOFTWARE LLP PROJECT PHASE 2 MILESTONE</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Fund Transfer</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -3088,7 +3097,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Payment to Nexgen Software LLP for project milestone via RTGS.</t>
         </is>
       </c>
       <c r="G62" t="b">
@@ -3098,73 +3107,73 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>1666</v>
+        <v>940400</v>
       </c>
       <c r="J62" t="n">
-        <v>3.42</v>
+        <v>5745010</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>07/09/2018</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>IMPS-825021548865-ARIF-HDFC-XXXXXXXXXXX0 366-COMMENTS</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>ARIF</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>Unknown description, possibly a person's name</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>1670</v>
-      </c>
-      <c r="J63" s="2" t="n">
-        <v>1673.42</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>12/09/2023</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>NEFT-AXIS0007890-LINKEDIN INDIA RECRUITMENT ADS SEP CAMPAIGN</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>NEFT AXIS0007890 LINKEDIN INDIA RECRUITMENT ADS SEP CAMPAIGN</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>E-Commerce &amp; Retail</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Payment to LinkedIn India for recruitment ads via NEFT.</t>
+        </is>
+      </c>
+      <c r="G63" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>32000</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>5713010</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08/09/2018</t>
+          <t>15/09/2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CC000489377XXXXXX6183AUTOPAYSI-TAD</t>
+          <t>NEFT-SBIN0007654-ADVANCE TAX Q2 AY 2024-25 CHALLAN NO. 280</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>NEFT SBIN0007654 ADVANCE TAX Q2 AY 2024 25 CHALLAN NO 280</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Interest &amp; Dividends</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -3172,41 +3181,41 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Advance tax payment to SBI via NEFT.</t>
         </is>
       </c>
       <c r="G64" t="b">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>8841</v>
+        <v>155000</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>-7167.58</v>
+        <v>5558010</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08/09/2018</t>
+          <t>18/09/2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CC000489377XXXXXX6183AUTOPAYSI-TAD</t>
+          <t>IMPS-230918026-CLEARTRIP BIZ FLT MUM-CHN 3 PAX ANNUAL REVIEW</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>CLEARTRIP BIZ FLT MUM CHN 3 PAX ANNUAL REVIEW</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Travel &amp; Transport</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -3214,41 +3223,41 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Business flight booking for annual review via Cleartrip.</t>
         </is>
       </c>
       <c r="G65" t="b">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>24500</v>
       </c>
       <c r="I65" t="n">
-        <v>8841</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>1673.42</v>
+        <v>5533510</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08/09/2018</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CC000489377XXXXXX6183AUTOPAYSI-TAD</t>
+          <t>NEFT-HDFC0001234-ELECBILL MSEDCL ELECTRICITY BILL SEP-2023</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>NEFT HDFC0001234 ELECBILL MSEDCL ELECTRICITY BILL SEP 2023</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -3256,41 +3265,41 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Electricity bill payment to MSEDCL via NEFT.</t>
         </is>
       </c>
       <c r="G66" t="b">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>1387</v>
+        <v>26600</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>286.42</v>
+        <v>5506910</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10/09/2018</t>
+          <t>25/09/2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>UKARHEALTHCAR-SALAUG.SIZWAN</t>
+          <t>CC 000789456XXXXXX2341 AUTOPAY-TAD CORPORATE CARD STMT SEP</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SALARY SIZWAN</t>
+          <t>CREDIT CARD AUTOPAY TAD CORPORATE CARD STMT SEP</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Credit Card Repayment</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -3298,120 +3307,120 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Exact match with payroll category definition</t>
+          <t>Autopay payment towards corporate credit card dues.</t>
         </is>
       </c>
       <c r="G67" t="b">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>81900</v>
       </c>
       <c r="I67" t="n">
-        <v>11690</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>11976.42</v>
+        <v>5425010</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>11/09/2018</t>
+          <t>28/09/2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCARE.PO POS DEBIT</t>
+          <t>NEFT-HDFC0009012-PRIMECAB CORPORATE CAB SERVICES Q2 — STAFF</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>UKARHEALTHCARE PO</t>
+          <t>NEFT HDFC0009012 PRIMECAB CORPORATE CAB SERVICES Q2 — STAFF</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Fund Transfer</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Description contains 'HEALTHCARE' indicating medical supplier</t>
+          <t>Payment to Primecab for corporate cab services via NEFT.</t>
         </is>
       </c>
       <c r="G68" t="b">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>2500</v>
+        <v>48000</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>9476.42</v>
+        <v>5377010</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>11/09/2018</t>
+          <t>30/09/2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NWD-541919XXXXXX3608-AND9013-NEWDELHI</t>
+          <t>CREDIT INTEREST CAPITALISED LIMITED</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL NEWDELHI</t>
+          <t>CREDIT INTEREST CAPITALISED LIMITED</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Loan &amp; EMI</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>Credit interest capitalized likely includes a loan or EMI</t>
         </is>
       </c>
       <c r="G69" t="b">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="J69" t="n">
-        <v>7976.42</v>
+        <v>5384210</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>12/09/2018</t>
+          <t>02/10/2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FUNDTRFDM-524181XXXXXX7263</t>
+          <t>NEFT-HDFC0000234-TECHPARK ESTATES LLP OFFICE RENT OCT-2023</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FUND TRANSFER</t>
+          <t>NEFT HDFC0000234 TECHPARK ESTATES LLP OFFICE RENT OCT 2023</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3424,41 +3433,41 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Internal transfer between own accounts</t>
+          <t>Office rent payment to Techpark Estates LLP via NEFT.</t>
         </is>
       </c>
       <c r="G70" t="b">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>1666</v>
+        <v>185000</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>6310.42</v>
+        <v>5199210</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>21/09/2018</t>
+          <t>04/10/2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NWD-541919XXXXXX3608-IPT8004-KAIMUR</t>
+          <t>RTGS-ICIC0000567-CLOUDINFRA SERVICES AWS USAGE BILL SEP CYCLE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL KAIMUR</t>
+          <t>RTGS ICIC0000567 CLOUDINFRA SERVICES AWS USAGE BILL SEP CYCLE</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -3466,167 +3475,167 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cash withdrawn from ATM in Kaimur</t>
+          <t>AWS usage bill payment to Cloudinfra Services via RTGS.</t>
         </is>
       </c>
       <c r="G71" t="b">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>500</v>
+        <v>382000</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>5810.42</v>
+        <v>4817210</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>23/09/2018</t>
+          <t>07/10/2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608AMAZONPAYPOSDEBI T</t>
+          <t>BULK NEFT-SALARY OCT-2023 5 EMPLOYEES + DIWALI BONUS Rs.50K EACH</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AMAZONPAYPOSDEBI</t>
+          <t>BULK NEFT SALARY OCT 2023 5 EMPLOYEES + DIWALI BONUS Rs 50K EACH</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>E-Commerce &amp; Retail</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Payment for online shopping on Amazon</t>
+          <t>Bulk salary payment to 5 employees with Diwali bonus via NEFT.</t>
         </is>
       </c>
       <c r="G72" t="b">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>130.72</v>
+        <v>655000</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>5679.7</v>
+        <v>4162210</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>24/09/2018</t>
+          <t>10/10/2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608ONE97COMMUNICATPO POS DEBIT</t>
+          <t>RTGS-HDFC0004365-NEXGEN SOFTWARE LLP AMD PAYMENT RECD — OCT INVOICE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PAYTMPO</t>
+          <t>RTGS HDFC0004365 NEXGEN SOFTWARE LLP AMD PAYMENT RECD — OCT INVOICE</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>E-Commerce &amp; Retail</t>
+          <t>Fund Transfer</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Paytm is a popular e-commerce and retail payment platform</t>
+          <t>Payment to Nexgen Software LLP for AMD payment via RTGS.</t>
         </is>
       </c>
       <c r="G73" t="b">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="J73" t="n">
-        <v>4679.7</v>
+        <v>5962210</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>26/09/2018</t>
+          <t>12/10/2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EAW-541919XXXXXX3608-TPCN1146-DELHI</t>
+          <t>NEFT-ICIC0009876-DIGITAL SPARK MEDIA DIWALI CAMPAIGN OCT-NOV</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL DELHI</t>
+          <t>NEFT ICIC0009876 DIGITAL SPARK MEDIA DIWALI CAMPAIGN OCT NOV</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>Payment to Digital Spark Media for Diwali campaign via NEFT.</t>
         </is>
       </c>
       <c r="G74" t="b">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>2000</v>
+        <v>120000</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>2679.7</v>
+        <v>5842210</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>28/09/2018</t>
+          <t>14/10/2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCAREPO POS DEBIT</t>
+          <t>IMPS-231014006-MARRIOTT HOTELS BIZ ACCOM TEAM RETREAT GOA 3D</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>UKARHEALTHCAREPO</t>
+          <t>MARRIOTT HOTELS BIZ ACCOM TEAM RETREAT GOA 3D</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Travel &amp; Transport</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -3634,335 +3643,335 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Purchase from medical supplier UKAR HEALTHCARE</t>
+          <t>Business accommodation booking for team retreat via Marriott Hotels.</t>
         </is>
       </c>
       <c r="G75" t="b">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>500</v>
+        <v>185000</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>2179.7</v>
+        <v>5657210</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>29/09/2018</t>
+          <t>16/10/2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608AIP*BHARTIAIRTEPO POS DEBIT</t>
+          <t>NEFT-HDFC0005678-JIRA/ATLASSIAN DEV TOOL ANNUAL RENEWAL</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BHARTIAIRTEPO</t>
+          <t>NEFT HDFC0005678 JIRA ATLASSIAN DEV TOOL ANNUAL RENEWAL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Utilities &amp; Telecom</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Payment for mobile recharge on Airtel</t>
+          <t>Annual renewal payment to Jira for Atlassian dev tool via NEFT.</t>
         </is>
       </c>
       <c r="G76" t="b">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>219</v>
+        <v>96000</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>1960.7</v>
+        <v>5561210</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>18/10/2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CREDITINTERESTCAPITALISED</t>
+          <t>NEFT-SBIN0007654-GST PAYMENT OCT-23 GSTN: 27AABCA1234B1Z5</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CREDITINTERESTCAPITALISED</t>
+          <t>NEFT SBIN0007654 GST PAYMENT OCT 23 GSTN: 27AABCA1234B1Z5</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Interest &amp; Dividends</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Description contains 'CREDITINTEREST' indicating credit card repayment</t>
+          <t>GST payment to SBI via NEFT.</t>
         </is>
       </c>
       <c r="G77" t="b">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>1981.7</v>
+        <v>5451210</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>04/10/2018</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>POS541919XXXXXX3608SURAKSHA,POSDEBIT</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>SURAKSHA,</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>Unknown description, possibly a person's name</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="2" t="n">
-        <v>1781.7</v>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20/10/2023</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>NEFT-HDFC0009012-INFRATECH MAINT SERVER ROOM AMC FY24 RENEWAL</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>NEFT HDFC0009012 INFRATECH MAINT SERVER ROOM AMC FY24 RENEWAL</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Fund Transfer</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Payment to Infratech for server room AMC via NEFT.</t>
+        </is>
+      </c>
+      <c r="G78" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>144000</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>5307210</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>04/10/2018</t>
+          <t>25/10/2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EAW-541919XXXXXX3608-DLON9519-NEWDELHI</t>
+          <t>CC 000789456XXXXXX2341 AUTOPAY-TAD CORPORATE CARD STMT OCT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL NEWDELHI</t>
+          <t>CREDIT CARD AUTOPAY TAD CORPORATE CARD STMT OCT</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Credit Card Repayment</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G79" t="b">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>500</v>
+        <v>92400</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>1281.7</v>
+        <v>5214810</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>04/10/2018</t>
+          <t>28/10/2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NWD-541919XXXXXX3608-S1CN4983-DELHI</t>
+          <t>NEFT-HDFC0001234-ELECBILL MSEDCL ELECTRICITY BILL OCT-2023</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL DELHI</t>
+          <t>NEFT HDFC0001234 ELECBILL MSEDCL ELECTRICITY BILL OCT 2023</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>Electricity bill payment via NEFT</t>
         </is>
       </c>
       <c r="G80" t="b">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>500</v>
+        <v>28200</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>781.7</v>
+        <v>5186610</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08/10/2018</t>
+          <t>31/10/2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CC000524181XXXXXX7263AUTOPAYSI-MAD</t>
+          <t>CREDIT INTEREST CAPITALISED</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>CREDIT INTEREST CAPITALISED</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Interest &amp; Dividends</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Credit interest capitalized indicates interest and dividend income.</t>
         </is>
       </c>
       <c r="G81" t="b">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>1914</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>8150</v>
       </c>
       <c r="J81" t="n">
-        <v>-1132.3</v>
+        <v>5194760</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08/10/2018</t>
+          <t>02/11/2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CC000524181XXXXXX7263AUTOPAYSI-MAD</t>
+          <t>NEFT-HDFC0000234-TECHPARK ESTATES LLP OFFICE RENT NOV-2023 LIMITED</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>NEFT HDFC0000234 TECHPARK ESTATES LLP OFFICE RENT NOV 2023 LIMITED</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Office rent payment via NEFT, unclear if retail</t>
         </is>
       </c>
       <c r="G82" t="b">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>185000</v>
       </c>
       <c r="I82" t="n">
-        <v>1914</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>781.7</v>
+        <v>5009760</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08/10/2018</t>
+          <t>04/11/2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCAREPO POS DEBIT</t>
+          <t>RTGS-ICIC0000567-CLOUDINFRA SERVICES AWS USAGE BILL OCT CYCLE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>UKARHEALTHCAREPO</t>
+          <t>RTGS ICIC0000567 CLOUDINFRA SERVICES AWS USAGE BILL OCT CYCLE</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -3970,41 +3979,41 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Purchase from medical supplier UKAR HEALTHCARE</t>
+          <t>AWS usage bill payment via RTGS</t>
         </is>
       </c>
       <c r="G83" t="b">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>100</v>
+        <v>415000</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>681.7</v>
+        <v>4594760</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09/10/2018</t>
+          <t>07/11/2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CC000489377XXXXXX6183AUTOPAYSI-TAD</t>
+          <t>BULK NEFT-SALARY NOV-2023 6 EMPLOYEES (NEW HIRE ADDED)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>BULK NEFT SALARY NOV 2023 6 EMPLOYEES (NEW HIRE ADDED)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -4012,49 +4021,49 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Bulk salary payment to employees via NEFT</t>
         </is>
       </c>
       <c r="G84" t="b">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>11848</v>
+        <v>495000</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>-11166.3</v>
+        <v>4099760</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09/10/2018</t>
+          <t>09/11/2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CC000489377XXXXXX6183AUTOPAYSI-TAD</t>
+          <t>RTGS-HDFC0004365-INFOZEAL TECH INC NOV RETAINER PAYMENT RECD</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>RTGS HDFC0004365 INFOZEAL TECH INC NOV RETAINER PAYMENT RECD</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Retainer payment via RTGS, unclear if retail</t>
         </is>
       </c>
       <c r="G85" t="b">
@@ -4064,73 +4073,73 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>11848</v>
+        <v>850000</v>
       </c>
       <c r="J85" t="n">
-        <v>681.7</v>
+        <v>4949760</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09/10/2018</t>
+          <t>12/11/2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CC000489377XXXXXX6183AUTOPAYSI-TAD</t>
+          <t>NEFT-AXIS0007890-LINKEDIN INDIA RECRUITMENT ADS NOV CAMPAIGN</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>NEFT AXIS0007890 LINKEDIN INDIA RECRUITMENT ADS NOV CAMPAIGN</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Recruitment ad payment via NEFT, unclear if retail</t>
         </is>
       </c>
       <c r="G86" t="b">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>1763</v>
+        <v>40000</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>-1081.3</v>
+        <v>4909760</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09/10/2018</t>
+          <t>14/11/2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CC000489377XXXXXX6183AUTOPAYSI-TAD</t>
+          <t>NEFT-HDFC0002345-HUBSPOT INDIA CRM PLATFORM ANNUAL LICENSE</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>NEFT HDFC0002345 HUBSPOT INDIA CRM PLATFORM ANNUAL LICENSE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -4138,125 +4147,125 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>CRM platform annual license payment via NEFT</t>
         </is>
       </c>
       <c r="G87" t="b">
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="I87" t="n">
-        <v>1763</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>681.7</v>
+        <v>4669760</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10/10/2018</t>
+          <t>16/11/2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>UKARHEALTHCAR-SALSEP.SIZWAN</t>
+          <t>IMPS-231116017-SPICE JET BUSINESS FLT MUM-DEL BUSINESS REVIEW MTG</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SALARY SIZWAN</t>
+          <t>SPICE JET BUSINESS FLT MUM DEL BUSINESS REVIEW MTG</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Travel &amp; Transport</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Exact match with payroll category definition</t>
+          <t>Business flight booking payment via NEFT</t>
         </is>
       </c>
       <c r="G88" t="b">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>22500</v>
       </c>
       <c r="I88" t="n">
-        <v>16690</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>17371.7</v>
+        <v>4647260</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>11/10/2018</t>
+          <t>18/11/2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FUNDTRFDM-489377XXXXXX6183</t>
+          <t>NEFT-SBIN0007654-GST PAYMENT NOV-23 GSTN: 27AABCA1234B1Z5</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FUND TRANSFER</t>
+          <t>NEFT SBIN0007654 GST PAYMENT NOV 23 GSTN: 27AABCA1234B1Z5</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Fund Transfer</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Internal transfer between own accounts</t>
+          <t>GST payment via NEFT, unclear if telecom</t>
         </is>
       </c>
       <c r="G89" t="b">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>11848</v>
+        <v>120000</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>5523.7</v>
+        <v>4527260</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>11/10/2018</t>
+          <t>20/11/2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FUNDTRFDM-524181XXXXXX7263</t>
+          <t>NEFT-HDFC0006789-FRESHWORKS INDIA HELP DESK TOOL ANNUAL PLAN</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FUND TRANSFER</t>
+          <t>NEFT HDFC0006789 FRESHWORKS INDIA HELP DESK TOOL ANNUAL PLAN</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Fund Transfer</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -4264,293 +4273,293 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Internal transfer between own accounts</t>
+          <t>Help desk tool annual plan payment via NEFT</t>
         </is>
       </c>
       <c r="G90" t="b">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>1293.33</v>
+        <v>108000</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>4230.37</v>
+        <v>4419260</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>12/10/2018</t>
+          <t>25/11/2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NWD-541919XXXXXX3608-SPCND016-NEWDELHI</t>
+          <t>CC 000789456XXXXXX2341 AUTOPAY-TAD CORPORATE CARD STMT NOV</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL NEWDELHI</t>
+          <t>CREDIT CARD AUTOPAY TAD CORPORATE CARD STMT NOV</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Credit Card Repayment</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>Autopay payment towards credit card dues</t>
         </is>
       </c>
       <c r="G91" t="b">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>3500</v>
+        <v>104800</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>730.37</v>
+        <v>4314460</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>14/10/2018</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>UPI-002261100000025-Q57945297@YBL-828788 602844-PAYMENTFROMPHONEPE</t>
+          <t>CREDIT INTEREST CAPITALISED</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>UPI TRANSFER</t>
+          <t>CREDIT INTEREST CAPITALISED</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>UPI &amp; Digital Payment</t>
+          <t>Interest &amp; Dividends</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Generic UPI transfer to unknown merchant</t>
+          <t>Credit interest capitalized indicates interest and dividend income.</t>
         </is>
       </c>
       <c r="G92" t="b">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>6780</v>
       </c>
       <c r="J92" t="n">
-        <v>679.37</v>
+        <v>4321240</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>16/10/2018</t>
+          <t>02/12/2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FEE-ATMCASH(1TXN)13/10/18-AOR1828962721AOR1828962721388 388</t>
+          <t>NEFT-HDFC0000234-TECHPARK ESTATES LLP OFFICE RENT DEC-2023</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BANK FEE ATMCASH 388</t>
+          <t>NEFT HDFC0000234 TECHPARK ESTATES LLP OFFICE RENT DEC 2023</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Bank Charges &amp; Fees</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ATM usage fee of Rs. 388</t>
+          <t>Office rent payment via NEFT, unclear if retail</t>
         </is>
       </c>
       <c r="G93" t="b">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>23.6</v>
+        <v>185000</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>655.77</v>
+        <v>4136240</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>21/10/2018</t>
+          <t>04/12/2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NWD-541919XXXXXX3608-S1CN4983-DELHI</t>
+          <t>RTGS-ICIC0000567-CLOUDINFRA SERVICES AWS USAGE BILL NOV CYCLE</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL DELHI</t>
+          <t>RTGS ICIC0000567 CLOUDINFRA SERVICES AWS USAGE BILL NOV CYCLE</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>AWS usage bill payment via RTGS</t>
         </is>
       </c>
       <c r="G94" t="b">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>500</v>
+        <v>396000</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>155.77</v>
+        <v>3740240</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>22/10/2018</t>
+          <t>07/12/2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FEE-ATMCASH(1TXN)21/10/18-AOR1829583474AOR1829583474670 670</t>
+          <t>BULK NEFT-SALARY DEC-2023 6 EMPLOYEES PROCESSED LIMITED</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BANK FEE ATMCASH 670</t>
+          <t>BULK NEFT SALARY DEC 2023 6 EMPLOYEES PROCESSED LIMITED</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Bank Charges &amp; Fees</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ATM usage fee of Rs. 670</t>
+          <t>Bulk salary payment to employees via NEFT</t>
         </is>
       </c>
       <c r="G95" t="b">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>23.6</v>
+        <v>495000</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>132.17</v>
+        <v>3245240</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>22/10/2018</t>
+          <t>10/12/2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FEE-ATMNONCASH(1TXN)21/10/18-AOR182958AOR1829583545299 3545299</t>
+          <t>RTGS-HDFC0004365-NEXGEN SOFTWARE LLP YEAR END PROJECT PAYMENT RECD</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BANK FEE ATMNONCASH</t>
+          <t>RTGS HDFC0004365 NEXGEN SOFTWARE LLP YEAR END PROJECT PAYMENT RECD</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Bank Charges &amp; Fees</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Non-cash ATM usage fee</t>
+          <t>Year-end project payment via RTGS, unclear if retail</t>
         </is>
       </c>
       <c r="G96" t="b">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>10.04</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>847900</v>
       </c>
       <c r="J96" t="n">
-        <v>122.13</v>
+        <v>4093140</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>27/10/2018</t>
+          <t>12/12/2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>UPI-002261100000025-Q91067891@YBL-830040 775595-PAYMENTFROMPHONEPE</t>
+          <t>NEFT-AXIS0001234-PR NEWSWIRE INDIA PRESS RELEASE ANNUAL PACKAGE</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>UPI TRANSFER</t>
+          <t>NEFT AXIS0001234 PR NEWSWIRE INDIA PRESS RELEASE ANNUAL PACKAGE</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>UPI &amp; Digital Payment</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -4558,41 +4567,41 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Generic UPI transfer to unknown merchant</t>
+          <t>Press release payment via NEFT, unclear if retail</t>
         </is>
       </c>
       <c r="G97" t="b">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>10.5</v>
+        <v>75000</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>111.63</v>
+        <v>4018140</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>27/10/2018</t>
+          <t>15/12/2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>UPI-002261100000025-Q91067891@YBL-830021 854654-PAYMENTFROMPHONEPE</t>
+          <t>NEFT-SBIN0007654-ADVANCE TAX Q3 AY 2024-25 CHALLAN NO. 280</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>UPI TRANSFER</t>
+          <t>NEFT SBIN0007654 ADVANCE TAX Q3 AY 2024 25 CHALLAN NO 280</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>UPI &amp; Digital Payment</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -4600,83 +4609,83 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Generic UPI transfer to unknown merchant</t>
+          <t>Advance tax payment via NEFT, unclear if telecom</t>
         </is>
       </c>
       <c r="G98" t="b">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>21</v>
+        <v>170000</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>90.63</v>
+        <v>3848140</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>03/11/2018</t>
+          <t>18/12/2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>UKARHEALTHCAR-SALOCT.SIZWAN</t>
+          <t>NEFT-HDFC0007890-OFFICESPACE RENO PARTITION &amp; INTERIORS PHASE 2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SALARY SIZWAN</t>
+          <t>NEFT HDFC0007890 OFFICESPACE RENO PARTITION &amp; INTERIORS PHASE 2</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Exact match with payroll category definition</t>
+          <t>Office renovation payment via NEFT, unclear if retail</t>
         </is>
       </c>
       <c r="G99" t="b">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="I99" t="n">
-        <v>16690</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>16780.63</v>
+        <v>3638140</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>03/11/2018</t>
+          <t>20/12/2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608TPS*PHONEPERECHPO POS DEBIT</t>
+          <t>IMPS-231220027-THOMAS COOK BIZ ANNUAL TEAM OFFSITE PACKAGE</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PHONEPERECHPO</t>
+          <t>THOMAS COOK BIZ ANNUAL TEAM OFFSITE PACKAGE</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Utilities &amp; Telecom</t>
+          <t>Travel &amp; Transport</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -4684,582 +4693,582 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>PhonePe is a mobile recharge and utility payment service</t>
+          <t>Annual team offsite package payment via NEFT</t>
         </is>
       </c>
       <c r="G100" t="b">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>139</v>
+        <v>150000</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>16641.63</v>
+        <v>3488140</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>05/11/2018</t>
+          <t>22/12/2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608BESTDEAL,POSDEBI T</t>
+          <t>NEFT-HDFC0001234-ELECBILL MSEDCL ELECTRICITY BILL DEC-2023</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BESTDEAL,POSDEBI</t>
+          <t>NEFT HDFC0001234 ELECBILL MSEDCL ELECTRICITY BILL DEC 2023</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>E-Commerce &amp; Retail</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Online shopping transaction from BestDeal</t>
+          <t>Electricity bill payment to MSEDCL via HDFC Bank</t>
         </is>
       </c>
       <c r="G101" t="b">
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>30400</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>16640.63</v>
+        <v>3457740</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>06/11/2018</t>
+          <t>25/12/2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCAREPO POS DEBIT</t>
+          <t>CC 000789456XXXXXX2341 AUTOPAY-TAD CORPORATE CARD STMT DEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>UKARHEALTHCAREPO</t>
+          <t>CREDIT CARD AUTOPAY TAD CORPORATE CARD STMT DEC</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Credit Card Repayment</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Purchase from medical supplier UKAR HEALTHCARE</t>
+          <t>Autopay payment for TAD Corporate Card statement</t>
         </is>
       </c>
       <c r="G102" t="b">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>300</v>
+        <v>88000</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>16340.63</v>
+        <v>3369740</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>06/11/2018</t>
+          <t>31/12/2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>UPI-002261100000025-Q91067891@YBL-831063 094070-PAYMENTFROMPHONEPE</t>
+          <t>CREDIT INTEREST CAPITALISED LIMITED</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>UPI TRANSFER</t>
+          <t>CREDIT INTEREST CAPITALISED LIMITED</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>UPI &amp; Digital Payment</t>
+          <t>Loan &amp; EMI</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Generic UPI transfer to unknown merchant</t>
+          <t>Credit interest capitalized likely includes a loan or EMI</t>
         </is>
       </c>
       <c r="G103" t="b">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="J103" t="n">
-        <v>16335.63</v>
+        <v>3374940</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>07/11/2018</t>
+          <t>02/01/2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CC000524181XXXXXX7263AUTOPAYSI-MAD</t>
+          <t>NEFT-HDFC0000234-TECHPARK ESTATES LLP OFFICE RENT JAN-2024</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>NEFT HDFC0000234 TECHPARK ESTATES LLP OFFICE RENT JAN 2024</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Office rent payment to Techpark Estates LLP via HDFC Bank</t>
         </is>
       </c>
       <c r="G104" t="b">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>2283</v>
+        <v>185000</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>14052.63</v>
+        <v>3189940</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>07/11/2018</t>
+          <t>04/01/2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>POS541919XXXXXX3608UKARHEALTHCAREPO POS DEBIT</t>
+          <t>RTGS-ICIC0000567-CLOUDINFRA SERVICES AWS USAGE BILL DEC CYCLE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>UKARHEALTHCAREPO</t>
+          <t>RTGS ICIC0000567 CLOUDINFRA SERVICES AWS USAGE BILL DEC CYCLE</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Purchase from medical supplier UKAR HEALTHCARE</t>
+          <t>AWS usage bill payment to Cloudinfra Services via ICICI Bank</t>
         </is>
       </c>
       <c r="G105" t="b">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>200</v>
+        <v>422000</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>13852.63</v>
+        <v>2767940</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>08/11/2018</t>
+          <t>07/01/2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CC000489377XXXXXX6183AUTOPAYSI-TAD</t>
+          <t>BULK NEFT-SALARY JAN-2024 6 EMP — POST-APPRAISAL REVISED CTCS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>BULK NEFT SALARY JAN 2024 6 EMP — POST APPRAISAL REVISED CTCS</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Bulk salary payment to 6 employees via HDFC Bank</t>
         </is>
       </c>
       <c r="G106" t="b">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>13299</v>
+        <v>550000</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>553.63</v>
+        <v>2217940</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>11/11/2018</t>
+          <t>10/01/2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>UPI-002261100000025-Q57945297@YBL-831511 603127-PAYMENTFROMPHONEPE</t>
+          <t>RTGS-HDFC0004365-NEXGEN SOFTWARE LLP Q4 NEW PROJECT ADVANCE RECD</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>UPI TRANSFER</t>
+          <t>RTGS HDFC0004365 NEXGEN SOFTWARE LLP Q4 NEW PROJECT ADVANCE RECD</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>UPI &amp; Digital Payment</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Generic UPI transfer to unknown merchant</t>
+          <t>Advance payment to Nexgen Software LLP for new project</t>
         </is>
       </c>
       <c r="G107" t="b">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>2200000</v>
       </c>
       <c r="J107" t="n">
-        <v>543.63</v>
+        <v>4417940</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>11/11/2018</t>
+          <t>12/01/2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>UPI-002261100000025-Q57945297@YBL-831544 652952-PAYMENTFROMPHONEPE</t>
+          <t>NEFT-ICIC0009876-DIGITAL SPARK MEDIA Q4 DIGITAL MARKETING RETAINER</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>UPI TRANSFER</t>
+          <t>NEFT ICIC0009876 DIGITAL SPARK MEDIA Q4 DIGITAL MARKETING RETAINER</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>UPI &amp; Digital Payment</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Generic UPI transfer to unknown merchant</t>
+          <t>Digital marketing retainer payment to Digital Spark Media</t>
         </is>
       </c>
       <c r="G108" t="b">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>20</v>
+        <v>60000</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>523.63</v>
+        <v>4357940</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>11/11/2018</t>
+          <t>14/01/2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>UPI-87782010129127-8506936041@YBL-831515 633807-PAYMENTFROMPHONEPE</t>
+          <t>NEFT-HDFC0005678-GITHUB ENTERPRISE ANNUAL DEV LICENCES — 20 SEATS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>UPI TRANSFER</t>
+          <t>NEFT HDFC0005678 GITHUB ENTERPRISE ANNUAL DEV LICENCES — 20 SEATS</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>UPI &amp; Digital Payment</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Generic UPI transfer to unknown merchant</t>
+          <t>Annual development licenses purchase for 20 seats from GitHub</t>
         </is>
       </c>
       <c r="G109" t="b">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>144000</v>
       </c>
       <c r="I109" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>1023.63</v>
+        <v>4213940</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>11/11/2018</t>
+          <t>16/01/2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>UPI-002261100000025-BILLDESKPP@YBL-83151 5740087-PAYMENTFROMPHONEPE</t>
+          <t>IMPS-240116007-AIR INDIA BUSINESS FLT MUM-SIN TECH SUMMIT 2 PAX</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>UPI TRANSFER</t>
+          <t>AIR INDIA BUSINESS FLT MUM SIN TECH SUMMIT 2 PAX</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>UPI &amp; Digital Payment</t>
+          <t>Travel &amp; Transport</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Generic UPI transfer to unknown merchant</t>
+          <t>Business flight booking for 2 passengers from Air India</t>
         </is>
       </c>
       <c r="G110" t="b">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>560</v>
+        <v>78000</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>463.63</v>
+        <v>4135940</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>14/11/2018</t>
+          <t>18/01/2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>UPI-002261100000025-Q91902894@YBL-831840 710520-PAYMENTFROMPHONEPE</t>
+          <t>NEFT-SBIN0007654-GST PAYMENT JAN-24 GSTN: 27AABCA1234B1Z5</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>UPI TRANSFER</t>
+          <t>NEFT SBIN0007654 GST PAYMENT JAN 24 GSTN: 27AABCA1234B1Z5</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>UPI &amp; Digital Payment</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Generic UPI transfer to unknown merchant</t>
+          <t>GST payment to SBI via HDFC Bank</t>
         </is>
       </c>
       <c r="G111" t="b">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>90</v>
+        <v>125000</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>373.63</v>
+        <v>4010940</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>18/11/2018</t>
+          <t>20/01/2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>UPI-002261100000025-EURONET@YBL-83224887 1857-PAYMENTFROMPHONEPE</t>
+          <t>NEFT-HDFC0009876-DELL INDIA 20 LAPTOP REFRESH Q4 CAPEX</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>UPI TRANSFER</t>
+          <t>NEFT HDFC0009876 DELL INDIA 20 LAPTOP REFRESH Q4 CAPEX</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>UPI &amp; Digital Payment</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Generic UPI transfer to unknown merchant</t>
+          <t>Laptop refresh purchase from Dell India via HDFC Bank</t>
         </is>
       </c>
       <c r="G112" t="b">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>127.95</v>
+        <v>580000</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>245.68</v>
+        <v>3430940</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>18/11/2018</t>
+          <t>22/01/2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>UPI-002261100000025-Q91067891@YBL-832221 875480-PAYMENTFROMPHONEPE</t>
+          <t>RTGS-KOTAK0001122-NETPLUS ILINK INTERNET BANDWIDTH UPGRADE</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>UPI TRANSFER</t>
+          <t>RTGS KOTAK0001122 NETPLUS ILINK INTERNET BANDWIDTH UPGRADE</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>UPI &amp; Digital Payment</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Generic UPI transfer to unknown merchant</t>
+          <t>Internet bandwidth upgrade payment to Netplus Ilink</t>
         </is>
       </c>
       <c r="G113" t="b">
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>24.48</v>
+        <v>84000</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>221.2</v>
+        <v>3346940</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>05/12/2018</t>
+          <t>25/01/2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CC000481508XXXXXX4092AUTOPAYSI-TAD</t>
+          <t>CC 000789456XXXXXX2341 AUTOPAY-TAD CORPORATE CARD STMT JAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>CREDIT CARD AUTOPAY TAD CORPORATE CARD STMT JAN</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5268,263 +5277,263 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Autopay payment for TAD Corporate Card statement</t>
         </is>
       </c>
       <c r="G114" t="b">
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>1832</v>
+        <v>112000</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>-1610.8</v>
+        <v>3234940</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>05/12/2018</t>
+          <t>28/01/2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CC000481508XXXXXX4092AUTOPAYSI-TAD</t>
+          <t>NEFT-HDFC0001234-ELECBILL MSEDCL ELECTRICITY BILL JAN-2024</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>NEFT HDFC0001234 ELECBILL MSEDCL ELECTRICITY BILL JAN 2024</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Electricity bill payment to MSEDCL via HDFC Bank</t>
         </is>
       </c>
       <c r="G115" t="b">
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>32600</v>
       </c>
       <c r="I115" t="n">
-        <v>1832</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>221.2</v>
+        <v>3202340</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>05/12/2018</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CC000481508XXXXXX4092AUTOPAYSI-TAD</t>
+          <t>CREDIT INTEREST CAPITALISED LIMITED</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>CREDIT INTEREST CAPITALISED LIMITED</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Loan &amp; EMI</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Credit interest capitalized likely includes a loan or EMI</t>
         </is>
       </c>
       <c r="G116" t="b">
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>1832</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>4920</v>
       </c>
       <c r="J116" t="n">
-        <v>-1610.8</v>
+        <v>3207260</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>05/12/2018</t>
+          <t>02/02/2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CC000481508XXXXXX4092AUTOPAYSI-TAD</t>
+          <t>NEFT-HDFC0000234-TECHPARK ESTATES LLP OFFICE RENT FEB-2024</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>NEFT HDFC0000234 TECHPARK ESTATES LLP OFFICE RENT FEB 2024</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Office rent payment to Techpark Estates LLP via HDFC Bank</t>
         </is>
       </c>
       <c r="G117" t="b">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>185000</v>
       </c>
       <c r="I117" t="n">
-        <v>1832</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>221.2</v>
+        <v>3022260</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>08/12/2018</t>
+          <t>04/02/2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CC000524181XXXXXX7263AUTOPAYSI-MAD</t>
+          <t>RTGS-ICIC0000567-CLOUDINFRA SERVICES AWS USAGE BILL JAN CYCLE</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>RTGS ICIC0000567 CLOUDINFRA SERVICES AWS USAGE BILL JAN CYCLE</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>AWS usage bill payment to Cloudinfra Services via ICICI Bank</t>
         </is>
       </c>
       <c r="G118" t="b">
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>1866</v>
+        <v>448000</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>-1644.8</v>
+        <v>2574260</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>08/12/2018</t>
+          <t>07/02/2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CC000524181XXXXXX7263AUTOPAYSI-MAD</t>
+          <t>BULK NEFT-SALARY FEB-2024 6 EMPLOYEES PROCESSED</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>BULK NEFT SALARY FEB 2024 6 EMPLOYEES PROCESSED</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Bulk salary payment to 6 employees via HDFC Bank</t>
         </is>
       </c>
       <c r="G119" t="b">
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>550000</v>
       </c>
       <c r="I119" t="n">
-        <v>1866</v>
+        <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>221.2</v>
+        <v>2024260</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>08/12/2018</t>
+          <t>09/02/2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>UPI-044991800014164-9680598953@YBL-83426 3511119-PAYMENTFROMPHONEPE</t>
+          <t>RTGS-HDFC0004365-INFOZEAL TECH INC FEB RETAINER + MILESTONE RECD</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>UPI TRANSFER</t>
+          <t>RTGS HDFC0004365 INFOZEAL TECH INC FEB RETAINER + MILESTONE RECD</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>UPI &amp; Digital Payment</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Generic UPI transfer to unknown merchant</t>
+          <t>Retainer and milestone payment to Infozeal Tech Inc</t>
         </is>
       </c>
       <c r="G120" t="b">
@@ -5534,283 +5543,283 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>20</v>
+        <v>1186460</v>
       </c>
       <c r="J120" t="n">
-        <v>241.2</v>
+        <v>3210720</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>09/12/2018</t>
+          <t>12/02/2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CC000489377XXXXXX6183AUTOPAYSI-TAD</t>
+          <t>NEFT-AXIS0007890-LINKEDIN INDIA RECRUITMENT DRIVE FEB-MAR</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>NEFT AXIS0007890 LINKEDIN INDIA RECRUITMENT DRIVE FEB MAR</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Recruitment drive payment to LinkedIn India</t>
         </is>
       </c>
       <c r="G121" t="b">
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>14078</v>
+        <v>55000</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>-13836.8</v>
+        <v>3155720</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>09/12/2018</t>
+          <t>14/02/2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CC000489377XXXXXX6183AUTOPAYSI-TAD</t>
+          <t>NEFT-HDFC0003456-DATADOG INC INFRA MONITORING ANNUAL PLAN</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>NEFT HDFC0003456 DATADOG INC INFRA MONITORING ANNUAL PLAN</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Annual infrastructure monitoring plan purchase from Datadog Inc</t>
         </is>
       </c>
       <c r="G122" t="b">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>192000</v>
       </c>
       <c r="I122" t="n">
-        <v>14078</v>
+        <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>241.2</v>
+        <v>2963720</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>09/12/2018</t>
+          <t>16/02/2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CC000489377XXXXXX6183AUTOPAYSI-TAD</t>
+          <t>IMPS-240216018-HYATT HOTELS BIZ ACCOM PUNE CLIENT PRESENTATION</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>HYATT HOTELS BIZ ACCOM PUNE CLIENT PRESENTATION</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Travel &amp; Transport</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>IRCTC train ticket or travel agent payment</t>
         </is>
       </c>
       <c r="G123" t="b">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>1647</v>
+        <v>38500</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>-1405.8</v>
+        <v>2925220</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>09/12/2018</t>
+          <t>18/02/2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CC000489377XXXXXX6183AUTOPAYSI-TAD</t>
+          <t>NEFT-SBIN0007654-GST PAYMENT FEB-24 GSTN: 27AABCA1234B1Z5</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>NEFT SBIN0007654 GST PAYMENT FEB 24 GSTN: 27AABCA1234B1Z5</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>GST payment for utility or telecom services</t>
         </is>
       </c>
       <c r="G124" t="b">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>135000</v>
       </c>
       <c r="I124" t="n">
-        <v>1647</v>
+        <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>241.2</v>
+        <v>2790220</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>10/12/2018</t>
+          <t>20/02/2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>UKARHEALTHCAR-SALNOV.SIZWAN</t>
+          <t>NEFT-HDFC0007654-ERNST &amp; YOUNG LLP STATUTORY AUDIT FEES FY24</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SALARY SIZWAN</t>
+          <t>NEFT HDFC0007654 ERNST &amp; YOUNG LLP STATUTORY AUDIT FEES FY24</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Exact match with payroll category definition</t>
+          <t>Professional services for software or IT</t>
         </is>
       </c>
       <c r="G125" t="b">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>220000</v>
       </c>
       <c r="I125" t="n">
-        <v>18690</v>
+        <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>18931.2</v>
+        <v>2570220</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>10/12/2018</t>
+          <t>25/02/2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ATW-541919XXXXXX3608-S1ANDE02-NEWDELHI</t>
+          <t>CC 000789456XXXXXX2341 AUTOPAY-TAD CORPORATE CARD STMT FEB</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ATM WITHDRAWAL NEWDELHI</t>
+          <t>CREDIT CARD AUTOPAY TAD CORPORATE CARD STMT FEB</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ATM Withdrawal</t>
+          <t>Credit Card Repayment</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
+          <t>Autopay for credit card dues</t>
         </is>
       </c>
       <c r="G126" t="b">
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>15000</v>
+        <v>124500</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>3931.2</v>
+        <v>2445720</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>10/12/2018</t>
+          <t>29/02/2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CD-0001013810001354096-10-DEC-18</t>
+          <t>CREDIT INTEREST CAPITALISED</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CASH DEPOSIT 10 DEC 18</t>
+          <t>CREDIT INTEREST CAPITALISED</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Cash Deposit</t>
+          <t>Interest &amp; Dividends</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -5818,456 +5827,456 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Cash deposited into the account on 10 DEC 18</t>
+          <t>Credit interest capitalized indicates interest and dividend income.</t>
         </is>
       </c>
       <c r="G127" t="b">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>2281.61</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="J127" t="n">
-        <v>1649.59</v>
+        <v>2449820</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>12/12/2018</t>
+          <t>02/03/2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>FUNDTRFDM-489377XXXXXX6183</t>
+          <t>NEFT-HDFC0000234-TECHPARK ESTATES LLP OFFICE RENT MAR-2024</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>FUND TRANSFER</t>
+          <t>NEFT HDFC0000234 TECHPARK ESTATES LLP OFFICE RENT MAR 2024</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Fund Transfer</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Internal transfer between own accounts</t>
+          <t>Office rent payment for commercial property</t>
         </is>
       </c>
       <c r="G128" t="b">
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>1646.76</v>
+        <v>185000</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>2.83</v>
+        <v>2264820</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>04/03/2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CREDITINTERESTCAPITALISED</t>
+          <t>RTGS-ICIC0000567-CLOUDINFRA SERVICES AWS USAGE BILL FEB CYCLE LIMITED</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CREDITINTERESTCAPITALISED</t>
+          <t>RTGS ICIC0000567 CLOUDINFRA SERVICES AWS USAGE BILL FEB CYCLE LIMITED</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Description contains 'CREDITINTEREST' indicating credit card repayment</t>
+          <t>Cloud services payment for software or IT</t>
         </is>
       </c>
       <c r="G129" t="b">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>396000</v>
       </c>
       <c r="I129" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>15.83</v>
+        <v>1868820</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>05/01/2019</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>IMPS-900520721077-ARIF-HDFC-XXXXXXXXXXX0 366-COMMENTS</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>ARIF</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>Unknown description, possibly a person's name</t>
-        </is>
-      </c>
-      <c r="G130" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J130" s="2" t="n">
-        <v>16.83</v>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>07/03/2024</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>BULK NEFT-SALARY MAR-2024 6 EMPLOYEES + PERFORMANCE BONUS</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>BULK NEFT SALARY MAR 2024 6 EMPLOYEES + PERFORMANCE BONUS</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>90</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Salary payment for employees</t>
+        </is>
+      </c>
+      <c r="G130" t="b">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>620000</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>1248820</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>05/01/2019</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>IMPS-900520723338-ARIF-HDFC-XXXXXXXXXXX0 366-COMMENTS</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>ARIF</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>Unknown description, possibly a person's name</t>
-        </is>
-      </c>
-      <c r="G131" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" s="2" t="n">
-        <v>1831</v>
-      </c>
-      <c r="J131" s="2" t="n">
-        <v>1847.83</v>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>10/03/2024</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>RTGS-HDFC0004365-NEXGEN SOFTWARE LLP FINAL PROJECT SETTLEMENT RECD</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>RTGS HDFC0004365 NEXGEN SOFTWARE LLP FINAL PROJECT SETTLEMENT RECD</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Software &amp; IT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>90</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Professional services for software or IT</t>
+        </is>
+      </c>
+      <c r="G131" t="b">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>496400</v>
+      </c>
+      <c r="J131" t="n">
+        <v>1745220</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>05/01/2019</t>
+          <t>12/03/2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>CC000481508XXXXXX4092AUTOPAYSI-TAD</t>
+          <t>NEFT-AXIS0001234-PR NEWSWIRE INDIA ANNUAL REPORT PR PACKAGE</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>NEFT AXIS0001234 PR NEWSWIRE INDIA ANNUAL REPORT PR PACKAGE</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Purchase of commercial services or products</t>
         </is>
       </c>
       <c r="G132" t="b">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="I132" t="n">
-        <v>1913</v>
+        <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>3760.83</v>
+        <v>1660220</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>05/01/2019</t>
+          <t>14/03/2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>CC000481508XXXXXX4092AUTOPAYSI-TAD</t>
+          <t>NEFT-SBIN0007654-ADVANCE TAX Q4 AY 2024-25 FINAL INSTALMENT</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>NEFT SBIN0007654 ADVANCE TAX Q4 AY 2024 25 FINAL INSTALMENT</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Advance tax payment for utility or telecom services</t>
         </is>
       </c>
       <c r="G133" t="b">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>1913</v>
+        <v>100000</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>1847.83</v>
+        <v>1560220</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>07/01/2019</t>
+          <t>16/03/2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>CC000489377XXXXXX6183AUTOPAYSI-TAD</t>
+          <t>NEFT-HDFC0009012-SOFTLICENCE HUB ADOBE CREATIVE CLOUD 10 SEATS</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>NEFT HDFC0009012 SOFTLICENCE HUB ADOBE CREATIVE CLOUD 10 SEATS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Software subscription for creative services</t>
         </is>
       </c>
       <c r="G134" t="b">
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>15365</v>
+        <v>84000</v>
       </c>
       <c r="I134" t="n">
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>-13517.17</v>
+        <v>1476220</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>07/01/2019</t>
+          <t>18/03/2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CC000489377XXXXXX6183AUTOPAYSI-TAD</t>
+          <t>IMPS-240318028-MAKE MY TRIP BIZ FLT MUM-DEL ANNUAL CONF 3 PAX</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>MAKE MY TRIP BIZ FLT MUM DEL ANNUAL CONF 3 PAX</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Travel &amp; Transport</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Business flight booking for conference</t>
         </is>
       </c>
       <c r="G135" t="b">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>42000</v>
       </c>
       <c r="I135" t="n">
-        <v>15365</v>
+        <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>1847.83</v>
+        <v>1434220</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>07/01/2019</t>
+          <t>20/03/2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CC000524181XXXXXX7263AUTOPAYSI-MAD</t>
+          <t>NEFT-HDFC0001234-ELECBILL MSEDCL ELECTRICITY BILL MAR-2024</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>NEFT HDFC0001234 ELECBILL MSEDCL ELECTRICITY BILL MAR 2024</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Electricity bill payment for commercial property</t>
         </is>
       </c>
       <c r="G136" t="b">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>2076</v>
+        <v>34000</v>
       </c>
       <c r="I136" t="n">
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>-228.17</v>
+        <v>1400220</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>07/01/2019</t>
+          <t>22/03/2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>CC000524181XXXXXX7263AUTOPAYSI-MAD</t>
+          <t>NEFT-HDFC0007654-FINTAX ADVISORY ROC FILING + COMPLIANCE FY24</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>NEFT HDFC0007654 FINTAX ADVISORY ROC FILING + COMPLIANCE FY24</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Professional services for software or IT</t>
         </is>
       </c>
       <c r="G137" t="b">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="I137" t="n">
-        <v>2076</v>
+        <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>1847.83</v>
+        <v>1320220</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>07/01/2019</t>
+          <t>25/03/2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CC000489377XXXXXX6183AUTOPAYSI-TAD</t>
+          <t>CC 000789456XXXXXX2341 AUTOPAY-TAD CORPORATE CARD STMT MAR</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>CREDIT CARD AUTOPAY TAD CORPORATE CARD STMT MAR</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6280,49 +6289,49 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Autopay for credit card dues</t>
         </is>
       </c>
       <c r="G138" t="b">
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>2194</v>
+        <v>135820</v>
       </c>
       <c r="I138" t="n">
         <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>-346.17</v>
+        <v>1184400</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>07/01/2019</t>
+          <t>31/03/2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>CC000489377XXXXXX6183AUTOPAYSI-TAD</t>
+          <t>CREDIT INTEREST CAPITALISED LIMITED</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CREDIT CARD AUTOPAY</t>
+          <t>CREDIT INTEREST CAPITALISED LIMITED</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Loan &amp; EMI</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Credit interest capitalized likely includes a loan or EMI</t>
         </is>
       </c>
       <c r="G139" t="b">
@@ -6332,1480 +6341,10 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>2194</v>
+        <v>3920</v>
       </c>
       <c r="J139" t="n">
-        <v>1847.83</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>08/01/2019</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>CD-0001013810001354096-08-JAN-19</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>CASH DEPOSIT 08 JAN 19</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Cash Deposit</t>
-        </is>
-      </c>
-      <c r="E140" t="n">
-        <v>90</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Cash deposited into the account on 08 JAN 19</t>
-        </is>
-      </c>
-      <c r="G140" t="b">
-        <v>0</v>
-      </c>
-      <c r="H140" t="n">
-        <v>1847.83</v>
-      </c>
-      <c r="I140" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>09/01/2019</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>UKARHEALTHCAR-SALDEC.SIZWAN</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>SALARY SIZWAN</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Payroll</t>
-        </is>
-      </c>
-      <c r="E141" t="n">
-        <v>100</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Exact match with payroll category definition</t>
-        </is>
-      </c>
-      <c r="G141" t="b">
-        <v>0</v>
-      </c>
-      <c r="H141" t="n">
-        <v>0</v>
-      </c>
-      <c r="I141" t="n">
-        <v>15690</v>
-      </c>
-      <c r="J141" t="n">
-        <v>15690</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>10/01/2019</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>FUNDTRFDM-489377XXXXXX6183</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>FUND TRANSFER</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Fund Transfer</t>
-        </is>
-      </c>
-      <c r="E142" t="n">
-        <v>100</v>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Internal transfer between own accounts</t>
-        </is>
-      </c>
-      <c r="G142" t="b">
-        <v>0</v>
-      </c>
-      <c r="H142" t="n">
-        <v>15364.83</v>
-      </c>
-      <c r="I142" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" t="n">
-        <v>325.17</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>23/01/2019</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>UKARHEALTHCAR-SIZWAN_ADVANCE</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>SALARY ADVANCE</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Payroll</t>
-        </is>
-      </c>
-      <c r="E143" t="n">
-        <v>90</v>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Advance salary payment to employees</t>
-        </is>
-      </c>
-      <c r="G143" t="b">
-        <v>0</v>
-      </c>
-      <c r="H143" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" t="n">
-        <v>30000</v>
-      </c>
-      <c r="J143" t="n">
-        <v>30325.17</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>23/01/2019</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>NWD-541919XXXXXX3608-SPCND016-NEWDELHI</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>ATM WITHDRAWAL NEWDELHI</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>ATM Withdrawal</t>
-        </is>
-      </c>
-      <c r="E144" t="n">
-        <v>95</v>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
-        </is>
-      </c>
-      <c r="G144" t="b">
-        <v>0</v>
-      </c>
-      <c r="H144" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I144" t="n">
-        <v>0</v>
-      </c>
-      <c r="J144" t="n">
-        <v>28825.17</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>25/01/2019</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>FEE-ATMCASH(1TXN)24/01/19-AOR1902565299AOR1902565299805 805</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>BANK FEE ATMCASH 805</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Bank Charges &amp; Fees</t>
-        </is>
-      </c>
-      <c r="E145" t="n">
-        <v>90</v>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>ATM usage fee charged by the bank</t>
-        </is>
-      </c>
-      <c r="G145" t="b">
-        <v>0</v>
-      </c>
-      <c r="H145" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="I145" t="n">
-        <v>0</v>
-      </c>
-      <c r="J145" t="n">
-        <v>28801.57</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>26/01/2019</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>ATW-541919XXXXXX3608-S1ANDL18-WESTDELHI</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>ATM WITHDRAWAL WESTDELHI</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>ATM Withdrawal</t>
-        </is>
-      </c>
-      <c r="E146" t="n">
-        <v>90</v>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Cash withdrawn from ATM in West Delhi</t>
-        </is>
-      </c>
-      <c r="G146" t="b">
-        <v>0</v>
-      </c>
-      <c r="H146" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I146" t="n">
-        <v>0</v>
-      </c>
-      <c r="J146" t="n">
-        <v>8801.57</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>26/01/2019</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>ATW-541919XXXXXX3608-S1ANDL18-WESTDELHI</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>ATM WITHDRAWAL WESTDELHI</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>ATM Withdrawal</t>
-        </is>
-      </c>
-      <c r="E147" t="n">
-        <v>90</v>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Cash withdrawn from ATM in West Delhi</t>
-        </is>
-      </c>
-      <c r="G147" t="b">
-        <v>0</v>
-      </c>
-      <c r="H147" t="n">
-        <v>500</v>
-      </c>
-      <c r="I147" t="n">
-        <v>0</v>
-      </c>
-      <c r="J147" t="n">
-        <v>8301.57</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>29/01/2019</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>UPI-002261100000025-TPSLCARD@YBL-9029804 56112-PAYMENTFROMPHONEPE</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>UPI TRANSFER</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>UPI &amp; Digital Payment</t>
-        </is>
-      </c>
-      <c r="E148" t="n">
-        <v>70</v>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Generic UPI transfer to unknown merchant</t>
-        </is>
-      </c>
-      <c r="G148" t="b">
-        <v>0</v>
-      </c>
-      <c r="H148" t="n">
-        <v>5978</v>
-      </c>
-      <c r="I148" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" t="n">
-        <v>2323.57</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>30/01/2019</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>POS541919XXXXXX3608PTM*IRCTCPOSDEBIT</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Travel &amp; Transport</t>
-        </is>
-      </c>
-      <c r="E149" t="n">
-        <v>90</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>IRCTC train ticket booking transaction</t>
-        </is>
-      </c>
-      <c r="G149" t="b">
-        <v>0</v>
-      </c>
-      <c r="H149" t="n">
-        <v>830.98</v>
-      </c>
-      <c r="I149" t="n">
-        <v>0</v>
-      </c>
-      <c r="J149" t="n">
-        <v>1492.59</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>02/02/2019</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>NWD-541919XXXXXX3608-S1CN4983-DELHI</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>ATM WITHDRAWAL DELHI</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>ATM Withdrawal</t>
-        </is>
-      </c>
-      <c r="E150" t="n">
-        <v>95</v>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
-        </is>
-      </c>
-      <c r="G150" t="b">
-        <v>0</v>
-      </c>
-      <c r="H150" t="n">
-        <v>500</v>
-      </c>
-      <c r="I150" t="n">
-        <v>0</v>
-      </c>
-      <c r="J150" t="n">
-        <v>992.59</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>04/02/2019</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>IMPS-903519615321-KGNRAILWAX-HDFC-XXXXX X4158-BENEFICIARYVERIFICATIONTRANSACTI ONONBEHALFOFC</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>KGNRAILWAX X4158 ON</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Travel &amp; Transport</t>
-        </is>
-      </c>
-      <c r="E151" t="n">
-        <v>90</v>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Train ticket booking transaction from KGN Railwax</t>
-        </is>
-      </c>
-      <c r="G151" t="b">
-        <v>0</v>
-      </c>
-      <c r="H151" t="n">
-        <v>0</v>
-      </c>
-      <c r="I151" t="n">
-        <v>1</v>
-      </c>
-      <c r="J151" t="n">
-        <v>993.59</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>04/02/2019</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>IMPS-903519615191-KGNRAILWAX-HDFC-XXXXX X4158-IMPSTRANSACTIONONBEHALFOFCUSTO MERSIWANALAMM</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>KGNRAILWAX X4158</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Travel &amp; Transport</t>
-        </is>
-      </c>
-      <c r="E152" t="n">
-        <v>90</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Train ticket booking transaction from KGN Railwax</t>
-        </is>
-      </c>
-      <c r="G152" t="b">
-        <v>0</v>
-      </c>
-      <c r="H152" t="n">
-        <v>0</v>
-      </c>
-      <c r="I152" t="n">
-        <v>1800</v>
-      </c>
-      <c r="J152" t="n">
-        <v>2793.59</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>04/02/2019</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>NWD-541919XXXXXX3608-S1CN4983-DELHI</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>ATM WITHDRAWAL DELHI</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>ATM Withdrawal</t>
-        </is>
-      </c>
-      <c r="E153" t="n">
-        <v>95</v>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
-        </is>
-      </c>
-      <c r="G153" t="b">
-        <v>0</v>
-      </c>
-      <c r="H153" t="n">
-        <v>700</v>
-      </c>
-      <c r="I153" t="n">
-        <v>0</v>
-      </c>
-      <c r="J153" t="n">
-        <v>2093.59</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>04/02/2019</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>IMPS-903520623469-KGNRAILWAX-HDFC-XXXXX X4158-IMPSTRANSACTIONONBEHALFOFCUSTO MERSIWANALAMM</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>KGNRAILWAX X4158</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Travel &amp; Transport</t>
-        </is>
-      </c>
-      <c r="E154" t="n">
-        <v>90</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Train ticket booking transaction from KGN Railwax</t>
-        </is>
-      </c>
-      <c r="G154" t="b">
-        <v>0</v>
-      </c>
-      <c r="H154" t="n">
-        <v>0</v>
-      </c>
-      <c r="I154" t="n">
-        <v>500</v>
-      </c>
-      <c r="J154" t="n">
-        <v>2593.59</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>05/02/2019</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>CC000481508XXXXXX4092AUTOPAYSI-TAD</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>CREDIT CARD AUTOPAY</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Credit Card Repayment</t>
-        </is>
-      </c>
-      <c r="E155" t="n">
-        <v>100</v>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Autopay payment towards credit card dues</t>
-        </is>
-      </c>
-      <c r="G155" t="b">
-        <v>0</v>
-      </c>
-      <c r="H155" t="n">
-        <v>2428</v>
-      </c>
-      <c r="I155" t="n">
-        <v>0</v>
-      </c>
-      <c r="J155" t="n">
-        <v>165.59</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>05/02/2019</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>CC000481508XXXXXX4092AUTOPAYSI-TAD</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>CREDIT CARD AUTOPAY</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Credit Card Repayment</t>
-        </is>
-      </c>
-      <c r="E156" t="n">
-        <v>100</v>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Autopay payment towards credit card dues</t>
-        </is>
-      </c>
-      <c r="G156" t="b">
-        <v>0</v>
-      </c>
-      <c r="H156" t="n">
-        <v>0</v>
-      </c>
-      <c r="I156" t="n">
-        <v>2428</v>
-      </c>
-      <c r="J156" t="n">
-        <v>2593.59</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>05/02/2019</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>CC000481508XXXXXX4092AUTOPAYSI-TAD</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>CREDIT CARD AUTOPAY</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Credit Card Repayment</t>
-        </is>
-      </c>
-      <c r="E157" t="n">
-        <v>100</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Autopay payment towards credit card dues</t>
-        </is>
-      </c>
-      <c r="G157" t="b">
-        <v>0</v>
-      </c>
-      <c r="H157" t="n">
-        <v>1862</v>
-      </c>
-      <c r="I157" t="n">
-        <v>0</v>
-      </c>
-      <c r="J157" t="n">
-        <v>731.59</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>07/02/2019</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>CC000524181XXXXXX7263AUTOPAYSI-MAD</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>CREDIT CARD AUTOPAY</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Credit Card Repayment</t>
-        </is>
-      </c>
-      <c r="E158" t="n">
-        <v>100</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Autopay payment towards credit card dues</t>
-        </is>
-      </c>
-      <c r="G158" t="b">
-        <v>0</v>
-      </c>
-      <c r="H158" t="n">
-        <v>2181</v>
-      </c>
-      <c r="I158" t="n">
-        <v>0</v>
-      </c>
-      <c r="J158" t="n">
-        <v>-1449.41</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>07/02/2019</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>CC000524181XXXXXX7263AUTOPAYSI-MAD</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>CREDIT CARD AUTOPAY</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Credit Card Repayment</t>
-        </is>
-      </c>
-      <c r="E159" t="n">
-        <v>100</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Autopay payment towards credit card dues</t>
-        </is>
-      </c>
-      <c r="G159" t="b">
-        <v>0</v>
-      </c>
-      <c r="H159" t="n">
-        <v>0</v>
-      </c>
-      <c r="I159" t="n">
-        <v>2181</v>
-      </c>
-      <c r="J159" t="n">
-        <v>731.59</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>16/02/2019</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>UPI-9910713305-9910713305@YBL-9047126641 80-PAYMENTFROMPHONEPE</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>UPI TRANSFER</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>UPI &amp; Digital Payment</t>
-        </is>
-      </c>
-      <c r="E160" t="n">
-        <v>70</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Generic UPI transfer to unknown merchant</t>
-        </is>
-      </c>
-      <c r="G160" t="b">
-        <v>0</v>
-      </c>
-      <c r="H160" t="n">
-        <v>10</v>
-      </c>
-      <c r="I160" t="n">
-        <v>0</v>
-      </c>
-      <c r="J160" t="n">
-        <v>721.59</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>17/02/2019</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>IMPS-904821002323-ABDULALI-HDFC-XXXXXXX XXXXXXXX3329-IMPSTXN</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>ABDULALI</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F161" s="2" t="inlineStr">
-        <is>
-          <t>Unknown transaction</t>
-        </is>
-      </c>
-      <c r="G161" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H161" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I161" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J161" s="2" t="n">
-        <v>722.59</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>17/02/2019</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>IMPS-904821003666-ABDUL-HDFC-XXXXXXXXX XXXXXX3329-IMPSTXN</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>ABDUL</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t>Unknown transaction</t>
-        </is>
-      </c>
-      <c r="G162" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I162" s="2" t="n">
-        <v>480</v>
-      </c>
-      <c r="J162" s="2" t="n">
-        <v>1202.59</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>18/02/2019</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>NWD-541919XXXXXX3608-S1CN4983-DELHI</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>ATM WITHDRAWAL DELHI</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>ATM Withdrawal</t>
-        </is>
-      </c>
-      <c r="E163" t="n">
-        <v>95</v>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Description contains 'ATM WITHDRAWAL' indicating cash withdrawal</t>
-        </is>
-      </c>
-      <c r="G163" t="b">
-        <v>0</v>
-      </c>
-      <c r="H163" t="n">
-        <v>600</v>
-      </c>
-      <c r="I163" t="n">
-        <v>0</v>
-      </c>
-      <c r="J163" t="n">
-        <v>602.59</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>04/03/2019</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>UPI-50100178092591-9953320743@YBL-906372 311971-PAYMENTFROMPHONEPE</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>UPI TRANSFER</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>UPI &amp; Digital Payment</t>
-        </is>
-      </c>
-      <c r="E164" t="n">
-        <v>70</v>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Generic UPI transfer to unknown merchant</t>
-        </is>
-      </c>
-      <c r="G164" t="b">
-        <v>0</v>
-      </c>
-      <c r="H164" t="n">
-        <v>0</v>
-      </c>
-      <c r="I164" t="n">
-        <v>500</v>
-      </c>
-      <c r="J164" t="n">
-        <v>1102.59</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>04/03/2019</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>UPI-50100178092591-9953320743@YBL-906318 499437-PAYMENTFROMPHONEPE</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>UPI TRANSFER</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>UPI &amp; Digital Payment</t>
-        </is>
-      </c>
-      <c r="E165" t="n">
-        <v>70</v>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Generic UPI transfer to unknown merchant</t>
-        </is>
-      </c>
-      <c r="G165" t="b">
-        <v>0</v>
-      </c>
-      <c r="H165" t="n">
-        <v>500</v>
-      </c>
-      <c r="I165" t="n">
-        <v>0</v>
-      </c>
-      <c r="J165" t="n">
-        <v>602.59</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>05/03/2019</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>CC000481508XXXXXX4092AUTOPAYSI-TAD</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>CREDIT CARD AUTOPAY</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Credit Card Repayment</t>
-        </is>
-      </c>
-      <c r="E166" t="n">
-        <v>100</v>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Autopay payment towards credit card dues</t>
-        </is>
-      </c>
-      <c r="G166" t="b">
-        <v>0</v>
-      </c>
-      <c r="H166" t="n">
-        <v>2398</v>
-      </c>
-      <c r="I166" t="n">
-        <v>0</v>
-      </c>
-      <c r="J166" t="n">
-        <v>-1795.41</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>05/03/2019</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>CC000481508XXXXXX4092AUTOPAYSI-TAD</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>CREDIT CARD AUTOPAY</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Credit Card Repayment</t>
-        </is>
-      </c>
-      <c r="E167" t="n">
-        <v>100</v>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Autopay payment towards credit card dues</t>
-        </is>
-      </c>
-      <c r="G167" t="b">
-        <v>0</v>
-      </c>
-      <c r="H167" t="n">
-        <v>0</v>
-      </c>
-      <c r="I167" t="n">
-        <v>2398</v>
-      </c>
-      <c r="J167" t="n">
-        <v>602.59</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>06/03/2019</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>CD-0001013810001354096-06-MAR-19</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>CASH DEPOSIT 06 MAR 19</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Cash Deposit</t>
-        </is>
-      </c>
-      <c r="E168" t="n">
-        <v>90</v>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Cash deposited into the account on 06 MAR 19</t>
-        </is>
-      </c>
-      <c r="G168" t="b">
-        <v>0</v>
-      </c>
-      <c r="H168" t="n">
-        <v>595.96</v>
-      </c>
-      <c r="I168" t="n">
-        <v>0</v>
-      </c>
-      <c r="J168" t="n">
-        <v>6.63</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>10/03/2019</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>CC000524181XXXXXX7263AUTOPAYSI-MAD</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>CREDIT CARD AUTOPAY</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>Credit Card Repayment</t>
-        </is>
-      </c>
-      <c r="E169" t="n">
-        <v>100</v>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>Autopay payment towards credit card dues</t>
-        </is>
-      </c>
-      <c r="G169" t="b">
-        <v>0</v>
-      </c>
-      <c r="H169" t="n">
-        <v>2211</v>
-      </c>
-      <c r="I169" t="n">
-        <v>0</v>
-      </c>
-      <c r="J169" t="n">
-        <v>-2204.37</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>10/03/2019</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>CC000524181XXXXXX7263AUTOPAYSI-MAD</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>CREDIT CARD AUTOPAY</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>Credit Card Repayment</t>
-        </is>
-      </c>
-      <c r="E170" t="n">
-        <v>100</v>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Autopay payment towards credit card dues</t>
-        </is>
-      </c>
-      <c r="G170" t="b">
-        <v>0</v>
-      </c>
-      <c r="H170" t="n">
-        <v>0</v>
-      </c>
-      <c r="I170" t="n">
-        <v>2211</v>
-      </c>
-      <c r="J170" t="n">
-        <v>6.63</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>18/03/2019</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>IMPS-907712395533-MOHAMMADKAUSAR-HDFC-X XXXXXXXXX0010-</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>MOHAMMADKAUSAR</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>Unknown transaction</t>
-        </is>
-      </c>
-      <c r="G171" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H171" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I171" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J171" s="2" t="n">
-        <v>1006.63</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>18/03/2019</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>CD-0001013810001354096-18-MAR-19</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>CASH DEPOSIT 18 MAR 19</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>Cash Deposit</t>
-        </is>
-      </c>
-      <c r="E172" t="n">
-        <v>90</v>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>Cash deposited into the account on 18 MAR 19</t>
-        </is>
-      </c>
-      <c r="G172" t="b">
-        <v>0</v>
-      </c>
-      <c r="H172" t="n">
-        <v>499.58</v>
-      </c>
-      <c r="I172" t="n">
-        <v>0</v>
-      </c>
-      <c r="J172" t="n">
-        <v>507.05</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>22/03/2019</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>ATW-541919XXXXXX3608-S1AWDE11-EASTDELHI</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>ATM WITHDRAWAL EASTDELHI</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>ATM Withdrawal</t>
-        </is>
-      </c>
-      <c r="E173" t="n">
-        <v>100</v>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>Cash withdrawn from ATM in East Delhi</t>
-        </is>
-      </c>
-      <c r="G173" t="b">
-        <v>0</v>
-      </c>
-      <c r="H173" t="n">
-        <v>500</v>
-      </c>
-      <c r="I173" t="n">
-        <v>0</v>
-      </c>
-      <c r="J173" t="n">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>01/04/2019</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>CREDITINTERESTCAPITALISED</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>CREDITINTERESTCAPITALISED</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Credit Card Repayment</t>
-        </is>
-      </c>
-      <c r="E174" t="n">
-        <v>80</v>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Description contains 'CREDITINTEREST' indicating credit card repayment</t>
-        </is>
-      </c>
-      <c r="G174" t="b">
-        <v>0</v>
-      </c>
-      <c r="H174" t="n">
-        <v>0</v>
-      </c>
-      <c r="I174" t="n">
-        <v>16</v>
-      </c>
-      <c r="J174" t="n">
-        <v>23.05</v>
+        <v>1188320</v>
       </c>
     </row>
   </sheetData>
@@ -7819,7 +6358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7844,7 +6383,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>₹5,541.09</t>
+          <t>₹1,842,350.00</t>
         </is>
       </c>
     </row>
@@ -7856,7 +6395,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>₹23.05</t>
+          <t>₹1,188,320.00</t>
         </is>
       </c>
     </row>
@@ -7868,7 +6407,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>₹325,737.33</t>
+          <t>₹18,838,540.00</t>
         </is>
       </c>
     </row>
@@ -7880,7 +6419,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>₹331,255.37</t>
+          <t>₹19,492,570.00</t>
         </is>
       </c>
     </row>
@@ -7892,7 +6431,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>₹-5,518.04</t>
+          <t>₹-654,030.00</t>
         </is>
       </c>
     </row>
@@ -7904,7 +6443,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>138</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -7931,264 +6470,207 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>166500</v>
+        <v>1034370</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-166500</v>
+        <v>-1034370</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bank Charges &amp; Fees</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>80.84</v>
+        <v>2740000</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1697900</v>
       </c>
       <c r="E9" t="n">
-        <v>-80.84</v>
+        <v>-1042100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cash Deposit</t>
+          <t>Fuel &amp; Auto</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>5224.98</v>
+        <v>370000</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-5224.98</v>
+        <v>-370000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Credit Card Repayment</t>
+          <t>Fund Transfer</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>98071</v>
+        <v>562000</v>
       </c>
       <c r="D11" t="n">
-        <v>78132</v>
+        <v>2740400</v>
       </c>
       <c r="E11" t="n">
-        <v>-19939</v>
+        <v>2178400</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E-Commerce &amp; Retail</t>
+          <t>Interest &amp; Dividends</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>1131.72</v>
+        <v>265000</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>40160</v>
       </c>
       <c r="E12" t="n">
-        <v>-1131.72</v>
+        <v>-224840</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fuel &amp; Auto</t>
+          <t>Loan &amp; EMI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>975</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>7.33</v>
+        <v>26220</v>
       </c>
       <c r="E13" t="n">
-        <v>-967.67</v>
+        <v>26220</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fund Transfer</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>31818.92</v>
+        <v>5552000</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-31818.92</v>
+        <v>-5552000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C15" t="n">
-        <v>18245</v>
+        <v>6436600</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>14333860</v>
       </c>
       <c r="E15" t="n">
-        <v>-18245</v>
+        <v>7897260</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Travel &amp; Transport</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>710100</v>
       </c>
       <c r="D16" t="n">
-        <v>189294</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>189294</v>
+        <v>-710100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Travel &amp; Transport</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>830.98</v>
+        <v>1822500</v>
       </c>
       <c r="D17" t="n">
-        <v>2301</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1470.02</v>
+        <v>-1822500</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>UPI &amp; Digital Payment</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>7407.93</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1020</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-6387.93</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>11</v>
-      </c>
-      <c r="C19" t="n">
-        <v>611</v>
-      </c>
-      <c r="D19" t="n">
-        <v>54983</v>
-      </c>
-      <c r="E19" t="n">
-        <v>54372</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Utilities &amp; Telecom</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2</v>
-      </c>
-      <c r="C20" t="n">
-        <v>358</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-358</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>── TOTAL ──</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n">
-        <v>173</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>331255.37</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>325737.33</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>-5518.04</v>
+      <c r="B18" s="9" t="n">
+        <v>138</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>19492570</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>18838540</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>-654030</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/clean_statement.xlsx
+++ b/data/output/clean_statement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Transactions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,10 +33,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00C00000"/>
     </font>
     <font>
       <b val="1"/>
@@ -56,7 +52,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -67,12 +63,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
         <bgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -100,23 +90,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -695,7 +681,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Software &amp; IT</t>
+          <t>Fund Transfer</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -703,7 +689,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nexgen Software LLP indicates a software and IT expense.</t>
+          <t>RTGS transaction to Nexgen Software LLP indicates a fund transfer.</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -913,7 +899,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Infosec Solutions cyber security audit fees indicate a software and IT expense.</t>
+          <t>Cyber security audit fees indicate a software and IT expense.</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -955,7 +941,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Credit card autopay indicates credit card repayment.</t>
+          <t>Credit card autopay indicates a credit card repayment.</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -997,7 +983,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fintax Advisory professional fees may involve e-commerce or retail expenses.</t>
+          <t>Fintax advisory professional fees may involve e-commerce or retail expenses.</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -1039,7 +1025,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Credit interest capitalized indicates interest and dividend income.</t>
+          <t>Interest capitalised on credit</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -1199,7 +1185,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Software &amp; IT</t>
+          <t>Fund Transfer</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1207,7 +1193,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nexgen Software LLP indicates a software and IT expense.</t>
+          <t>RTGS transaction to Nexgen Software LLP indicates a fund transfer.</t>
         </is>
       </c>
       <c r="G17" t="b">
@@ -1375,7 +1361,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ergodesk Solutions office furniture purchase may involve e-commerce or retail expenses.</t>
+          <t>Ergodesk solutions office furniture purchase may involve e-commerce or retail expenses.</t>
         </is>
       </c>
       <c r="G21" t="b">
@@ -1417,7 +1403,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leased line renewal indicates a software or IT service</t>
+          <t>Netplus ilink leased line renewal indicates a software and IT expense.</t>
         </is>
       </c>
       <c r="G22" t="b">
@@ -1459,7 +1445,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Autopay indicates a credit card repayment</t>
+          <t>Autopay payment towards corporate credit card dues</t>
         </is>
       </c>
       <c r="G23" t="b">
@@ -1501,7 +1487,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Credit interest capitalized indicates interest and dividend income.</t>
+          <t>Interest capitalised on credit</t>
         </is>
       </c>
       <c r="G24" t="b">
@@ -1535,15 +1521,15 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Utilities &amp; Telecom</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Office rent likely includes utilities or telecom services</t>
+          <t>Salary payment to Techpark Estates LLP for office rent</t>
         </is>
       </c>
       <c r="G25" t="b">
@@ -1581,11 +1567,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AWS usage indicates a software or IT service</t>
+          <t>Payment for AWS usage bill from Cloudinfra Services</t>
         </is>
       </c>
       <c r="G26" t="b">
@@ -1623,11 +1609,11 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bulk NEFT indicates a payroll transaction</t>
+          <t>Bulk salary payment to 4 employees of Limited</t>
         </is>
       </c>
       <c r="G27" t="b">
@@ -1665,11 +1651,11 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Software LLP indicates a software or IT service</t>
+          <t>Payment for Q1 project completion from Nexgen Software LLP</t>
         </is>
       </c>
       <c r="G28" t="b">
@@ -1707,11 +1693,11 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Recruitment ads likely include online advertising</t>
+          <t>Payment for LinkedIn India recruitment ads campaign</t>
         </is>
       </c>
       <c r="G29" t="b">
@@ -1749,11 +1735,11 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cleartrip indicates a travel or transport service</t>
+          <t>Business flight booking for sales team</t>
         </is>
       </c>
       <c r="G30" t="b">
@@ -1791,11 +1777,11 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GST payment likely includes utilities or telecom services</t>
+          <t>GST payment to SBI for June 2023</t>
         </is>
       </c>
       <c r="G31" t="b">
@@ -1833,11 +1819,11 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zendesk indicates a software or IT service</t>
+          <t>Annual license payment for Zendesk India support tool</t>
         </is>
       </c>
       <c r="G32" t="b">
@@ -1879,7 +1865,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Autopay indicates a credit card repayment</t>
+          <t>Autopay payment towards corporate credit card dues</t>
         </is>
       </c>
       <c r="G33" t="b">
@@ -1917,11 +1903,11 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Electricity bill indicates a utility or telecom service</t>
+          <t>Payment for June 2023 electricity bill from MSEDCL</t>
         </is>
       </c>
       <c r="G34" t="b">
@@ -1955,15 +1941,15 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Loan &amp; EMI</t>
+          <t>Interest &amp; Dividends</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Credit interest capitalized likely includes a loan or EMI</t>
+          <t>Capitalised interest for Limited</t>
         </is>
       </c>
       <c r="G35" t="b">
@@ -1980,44 +1966,44 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>03/07/2023</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>NEFT-HDFC0000234-TECHPARK ESTATES LLP OFFICE RENT JUL-2023</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>NEFT HDFC0000234 TECHPARK ESTATES LLP OFFICE RENT JUL 2023</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Fuel &amp; Auto</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Unable to determine category due to unclear description</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36" s="2" t="n">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Salary payment to Techpark Estates LLP for office rent</t>
+        </is>
+      </c>
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
         <v>185000</v>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="2" t="n">
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
         <v>3382530</v>
       </c>
     </row>
@@ -2043,11 +2029,11 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Strong match for Software &amp; IT category due to AWS usage</t>
+          <t>Payment for AWS usage bill from Cloudinfra Services</t>
         </is>
       </c>
       <c r="G37" t="b">
@@ -2085,11 +2071,11 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Clear match for Payroll category due to salary payment</t>
+          <t>Bulk salary payment to 5 employees including new hire Vikram Rao</t>
         </is>
       </c>
       <c r="G38" t="b">
@@ -2127,11 +2113,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Strong match for Software &amp; IT category due to software company</t>
+          <t>Advance payment for new project kickoff from Nexgen Software LLP</t>
         </is>
       </c>
       <c r="G39" t="b">
@@ -2169,11 +2155,11 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Probable match for E-Commerce &amp; Retail category due to Google Ads</t>
+          <t>Payment for Google ads management from Digital Spark Media</t>
         </is>
       </c>
       <c r="G40" t="b">
@@ -2211,11 +2197,11 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Strong match for Software &amp; IT category due to AWS purchase</t>
+          <t>Reserved instance purchase from AWS India Pvt Ltd</t>
         </is>
       </c>
       <c r="G41" t="b">
@@ -2253,11 +2239,11 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Probable match for Utilities &amp; Telecom category due to GST payment</t>
+          <t>GST payment to SBI for July 2023</t>
         </is>
       </c>
       <c r="G42" t="b">
@@ -2295,11 +2281,11 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Clear match for Travel &amp; Transport category due to airline booking</t>
+          <t>Business flight booking for 4 pax to Tech Summit</t>
         </is>
       </c>
       <c r="G43" t="b">
@@ -2337,11 +2323,11 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Probable match for E-Commerce &amp; Retail category due to membership fees</t>
+          <t>Membership fees paid to NASSCOM India</t>
         </is>
       </c>
       <c r="G44" t="b">
@@ -2379,11 +2365,11 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Clear match for Credit Card Repayment category due to autopay</t>
+          <t>Autopay payment for TAD corporate credit card</t>
         </is>
       </c>
       <c r="G45" t="b">
@@ -2425,7 +2411,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Clear match for Utilities &amp; Telecom category due to electricity bill</t>
+          <t>Electricity bill payment to MSEDCL</t>
         </is>
       </c>
       <c r="G46" t="b">
@@ -2467,7 +2453,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Credit interest capitalized indicates interest and dividend income.</t>
+          <t>Interest capitalised on credit</t>
         </is>
       </c>
       <c r="G47" t="b">
@@ -2484,44 +2470,44 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>02/08/2023</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>NEFT-HDFC0000234-TECHPARK ESTATES LLP OFFICE RENT AUG-2023 LIMITED</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>NEFT HDFC0000234 TECHPARK ESTATES LLP OFFICE RENT AUG 2023 LIMITED</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Fuel &amp; Auto</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Unable to determine category due to unclear description</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H48" s="2" t="n">
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>E-Commerce &amp; Retail</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>90</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Office rent payment to Techpark Estates LLP</t>
+        </is>
+      </c>
+      <c r="G48" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
         <v>185000</v>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="2" t="n">
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
         <v>3300250</v>
       </c>
     </row>
@@ -2551,7 +2537,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Strong match for Software &amp; IT category due to AWS usage</t>
+          <t>AWS usage bill payment to Cloudinfra Services</t>
         </is>
       </c>
       <c r="G49" t="b">
@@ -2589,11 +2575,11 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Clear match for Payroll category due to salary payment</t>
+          <t>Bulk salary payment to 5 employees</t>
         </is>
       </c>
       <c r="G50" t="b">
@@ -2627,15 +2613,15 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Software &amp; IT</t>
+          <t>IMPS Transfer</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Probable match for Software &amp; IT category due to software company</t>
+          <t>Client payment received in USD by Infozeal Tech Inc</t>
         </is>
       </c>
       <c r="G51" t="b">
@@ -2673,11 +2659,11 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Probable match for E-Commerce &amp; Retail category due to SEO services</t>
+          <t>SEO and social media services payment to Digital Spark Media</t>
         </is>
       </c>
       <c r="G52" t="b">
@@ -2719,7 +2705,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Strong match for Software &amp; IT category due to SAAS tool</t>
+          <t>Annual contract payment for SaaS tool to Episode Six Tech</t>
         </is>
       </c>
       <c r="G53" t="b">
@@ -2757,11 +2743,11 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Probable match for Utilities &amp; Telecom category due to GST payment</t>
+          <t>GST payment to SBI</t>
         </is>
       </c>
       <c r="G54" t="b">
@@ -2803,7 +2789,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Clear match for Travel &amp; Transport category due to hotel booking</t>
+          <t>Business accommodation booking at TAJ Hotels in Pune</t>
         </is>
       </c>
       <c r="G55" t="b">
@@ -2841,11 +2827,11 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Probable match for E-Commerce &amp; Retail category due to expo booth design</t>
+          <t>Expo booth design and branding services payment to Brand Elevate Co</t>
         </is>
       </c>
       <c r="G56" t="b">
@@ -2887,7 +2873,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Autopay payment towards corporate credit card dues.</t>
+          <t>Autopay payment for TAD corporate credit card</t>
         </is>
       </c>
       <c r="G57" t="b">
@@ -2929,7 +2915,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Credit interest capitalized indicates interest and dividend income.</t>
+          <t>Interest capitalised on credit</t>
         </is>
       </c>
       <c r="G58" t="b">
@@ -2963,15 +2949,15 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Fund Transfer</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Office rent payment to Techpark Estates LLP via NEFT.</t>
+          <t>Office rent payment to Techpark Estates LLP</t>
         </is>
       </c>
       <c r="G59" t="b">
@@ -3009,11 +2995,11 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AWS usage bill payment to Cloudinfra Services via RTGS.</t>
+          <t>AWS usage bill payment to Cloudinfra Services</t>
         </is>
       </c>
       <c r="G60" t="b">
@@ -3055,7 +3041,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bulk salary payment to 5 employees via NEFT.</t>
+          <t>Bulk salary payment to 5 employees</t>
         </is>
       </c>
       <c r="G61" t="b">
@@ -3089,15 +3075,15 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Fund Transfer</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Payment to Nexgen Software LLP for project milestone via RTGS.</t>
+          <t>Project milestone payment to Nexgen Software LLP</t>
         </is>
       </c>
       <c r="G62" t="b">
@@ -3135,11 +3121,11 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Payment to LinkedIn India for recruitment ads via NEFT.</t>
+          <t>Recruitment ads payment to LinkedIn India</t>
         </is>
       </c>
       <c r="G63" t="b">
@@ -3173,15 +3159,15 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Interest &amp; Dividends</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Advance tax payment to SBI via NEFT.</t>
+          <t>Advance tax payment to SBI</t>
         </is>
       </c>
       <c r="G64" t="b">
@@ -3219,11 +3205,11 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Business flight booking for annual review via Cleartrip.</t>
+          <t>Business flight booking from Mumbai to China</t>
         </is>
       </c>
       <c r="G65" t="b">
@@ -3261,11 +3247,11 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Electricity bill payment to MSEDCL via NEFT.</t>
+          <t>Electricity bill payment to MSEDCL via HDFC</t>
         </is>
       </c>
       <c r="G66" t="b">
@@ -3307,7 +3293,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Autopay payment towards corporate credit card dues.</t>
+          <t>Autopay payment for TAD corporate credit card</t>
         </is>
       </c>
       <c r="G67" t="b">
@@ -3341,15 +3327,15 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Fund Transfer</t>
+          <t>Travel &amp; Transport</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Payment to Primecab for corporate cab services via NEFT.</t>
+          <t>Cab services payment to Primecab for staff</t>
         </is>
       </c>
       <c r="G68" t="b">
@@ -3383,15 +3369,15 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Loan &amp; EMI</t>
+          <t>Interest &amp; Dividends</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Credit interest capitalized likely includes a loan or EMI</t>
+          <t>Capitalised interest for Limited</t>
         </is>
       </c>
       <c r="G69" t="b">
@@ -3425,15 +3411,15 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Fund Transfer</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Office rent payment to Techpark Estates LLP via NEFT.</t>
+          <t>Office rent payment to Techpark Estates LLP</t>
         </is>
       </c>
       <c r="G70" t="b">
@@ -3471,11 +3457,11 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AWS usage bill payment to Cloudinfra Services via RTGS.</t>
+          <t>AWS usage bill payment to Cloudinfra Services</t>
         </is>
       </c>
       <c r="G71" t="b">
@@ -3517,7 +3503,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bulk salary payment to 5 employees with Diwali bonus via NEFT.</t>
+          <t>Bulk salary payment to 5 employees with Diwali bonus</t>
         </is>
       </c>
       <c r="G72" t="b">
@@ -3551,15 +3537,15 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Fund Transfer</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Payment to Nexgen Software LLP for AMD payment via RTGS.</t>
+          <t>AMD payment received from Nexgen Software LLP</t>
         </is>
       </c>
       <c r="G73" t="b">
@@ -3597,11 +3583,11 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Payment to Digital Spark Media for Diwali campaign via NEFT.</t>
+          <t>Diwali campaign payment to Digital Spark Media</t>
         </is>
       </c>
       <c r="G74" t="b">
@@ -3639,11 +3625,11 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Business accommodation booking for team retreat via Marriott Hotels.</t>
+          <t>Business accommodation booking at Marriott Hotels</t>
         </is>
       </c>
       <c r="G75" t="b">
@@ -3681,11 +3667,11 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Annual renewal payment to Jira for Atlassian dev tool via NEFT.</t>
+          <t>Annual renewal payment for Jira Atlassian dev tool</t>
         </is>
       </c>
       <c r="G76" t="b">
@@ -3719,15 +3705,15 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Interest &amp; Dividends</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>GST payment to SBI via NEFT.</t>
+          <t>GST payment to SBI</t>
         </is>
       </c>
       <c r="G77" t="b">
@@ -3761,15 +3747,15 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Fund Transfer</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Payment to Infratech for server room AMC via NEFT.</t>
+          <t>Server room AMC payment to Infratech Maintenance</t>
         </is>
       </c>
       <c r="G78" t="b">
@@ -3811,7 +3797,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Autopay payment for TAD corporate credit card</t>
         </is>
       </c>
       <c r="G79" t="b">
@@ -3849,11 +3835,11 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Electricity bill payment via NEFT</t>
+          <t>Electricity bill payment to MSEDCL via HDFC</t>
         </is>
       </c>
       <c r="G80" t="b">
@@ -3895,7 +3881,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Credit interest capitalized indicates interest and dividend income.</t>
+          <t>Interest capitalised on credit</t>
         </is>
       </c>
       <c r="G81" t="b">
@@ -3933,11 +3919,11 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Office rent payment via NEFT, unclear if retail</t>
+          <t>Office rent payment to Techpark Estates LLP</t>
         </is>
       </c>
       <c r="G82" t="b">
@@ -3975,11 +3961,11 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AWS usage bill payment via RTGS</t>
+          <t>AWS usage bill payment to Cloudinfra Services</t>
         </is>
       </c>
       <c r="G83" t="b">
@@ -4021,7 +4007,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bulk salary payment to employees via NEFT</t>
+          <t>Bulk salary payment to 6 employees with new hire</t>
         </is>
       </c>
       <c r="G84" t="b">
@@ -4055,15 +4041,15 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>E-Commerce &amp; Retail</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Retainer payment via RTGS, unclear if retail</t>
+          <t>Retainer payment received from Infozeal Tech Inc</t>
         </is>
       </c>
       <c r="G85" t="b">
@@ -4101,11 +4087,11 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Recruitment ad payment via NEFT, unclear if retail</t>
+          <t>Recruitment ads payment to LinkedIn India</t>
         </is>
       </c>
       <c r="G86" t="b">
@@ -4143,11 +4129,11 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CRM platform annual license payment via NEFT</t>
+          <t>Annual license payment for Hubspot CRM platform</t>
         </is>
       </c>
       <c r="G87" t="b">
@@ -4189,7 +4175,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Business flight booking payment via NEFT</t>
+          <t>IRCTC train ticket purchase for business review meeting</t>
         </is>
       </c>
       <c r="G88" t="b">
@@ -4227,11 +4213,11 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>GST payment via NEFT, unclear if telecom</t>
+          <t>GST payment for telecom services</t>
         </is>
       </c>
       <c r="G89" t="b">
@@ -4269,11 +4255,11 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Help desk tool annual plan payment via NEFT</t>
+          <t>SaaS subscription for help desk tool</t>
         </is>
       </c>
       <c r="G90" t="b">
@@ -4311,11 +4297,11 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Autopay payment towards credit card dues</t>
+          <t>Autopay for corporate credit card statement</t>
         </is>
       </c>
       <c r="G91" t="b">
@@ -4357,7 +4343,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Credit interest capitalized indicates interest and dividend income.</t>
+          <t>Interest capitalised on credit</t>
         </is>
       </c>
       <c r="G92" t="b">
@@ -4395,11 +4381,11 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Office rent payment via NEFT, unclear if retail</t>
+          <t>Office rent payment for Techpark Estates LLP</t>
         </is>
       </c>
       <c r="G93" t="b">
@@ -4437,11 +4423,11 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>AWS usage bill payment via RTGS</t>
+          <t>Cloud services payment for AWS usage</t>
         </is>
       </c>
       <c r="G94" t="b">
@@ -4479,11 +4465,11 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bulk salary payment to employees via NEFT</t>
+          <t>Bulk salary payment for 6 employees</t>
         </is>
       </c>
       <c r="G95" t="b">
@@ -4517,15 +4503,15 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>E-Commerce &amp; Retail</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Year-end project payment via RTGS, unclear if retail</t>
+          <t>Payment for year-end project with Nexgen Software LLP</t>
         </is>
       </c>
       <c r="G96" t="b">
@@ -4563,11 +4549,11 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Press release payment via NEFT, unclear if retail</t>
+          <t>Annual press release package for PR Newswire India</t>
         </is>
       </c>
       <c r="G97" t="b">
@@ -4605,11 +4591,11 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Advance tax payment via NEFT, unclear if telecom</t>
+          <t>Advance tax payment for Q3 AY 2024</t>
         </is>
       </c>
       <c r="G98" t="b">
@@ -4647,11 +4633,11 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Office renovation payment via NEFT, unclear if retail</t>
+          <t>Office renovation payment for Officespace</t>
         </is>
       </c>
       <c r="G99" t="b">
@@ -4693,7 +4679,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Annual team offsite package payment via NEFT</t>
+          <t>Annual team offsite package for business</t>
         </is>
       </c>
       <c r="G100" t="b">
@@ -4731,11 +4717,11 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Electricity bill payment to MSEDCL via HDFC Bank</t>
+          <t>Electricity bill payment for MSEDCL</t>
         </is>
       </c>
       <c r="G101" t="b">
@@ -4773,11 +4759,11 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Autopay payment for TAD Corporate Card statement</t>
+          <t>Autopay for corporate credit card statement</t>
         </is>
       </c>
       <c r="G102" t="b">
@@ -4811,15 +4797,15 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Loan &amp; EMI</t>
+          <t>Interest &amp; Dividends</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Credit interest capitalized likely includes a loan or EMI</t>
+          <t>Capitalised interest for Limited</t>
         </is>
       </c>
       <c r="G103" t="b">
@@ -4857,11 +4843,11 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Office rent payment to Techpark Estates LLP via HDFC Bank</t>
+          <t>Office rent payment for Techpark Estates LLP</t>
         </is>
       </c>
       <c r="G104" t="b">
@@ -4899,11 +4885,11 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>AWS usage bill payment to Cloudinfra Services via ICICI Bank</t>
+          <t>Cloud services payment for AWS usage</t>
         </is>
       </c>
       <c r="G105" t="b">
@@ -4941,11 +4927,11 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bulk salary payment to 6 employees via HDFC Bank</t>
+          <t>Bulk salary payment for 6 employees post appraisal</t>
         </is>
       </c>
       <c r="G106" t="b">
@@ -4983,11 +4969,11 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Advance payment to Nexgen Software LLP for new project</t>
+          <t>Payment for new project advance with Nexgen Software LLP</t>
         </is>
       </c>
       <c r="G107" t="b">
@@ -5025,11 +5011,11 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Digital marketing retainer payment to Digital Spark Media</t>
+          <t>Digital marketing retainer payment for Digital Spark Media</t>
         </is>
       </c>
       <c r="G108" t="b">
@@ -5067,11 +5053,11 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Annual development licenses purchase for 20 seats from GitHub</t>
+          <t>Annual development licenses for 20 seats with GitHub Enterprise</t>
         </is>
       </c>
       <c r="G109" t="b">
@@ -5113,7 +5099,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Business flight booking for 2 passengers from Air India</t>
+          <t>IRCTC train ticket purchase for business travel</t>
         </is>
       </c>
       <c r="G110" t="b">
@@ -5151,11 +5137,11 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>GST payment to SBI via HDFC Bank</t>
+          <t>GST payment for telecom services, unclear if utility or telecom</t>
         </is>
       </c>
       <c r="G111" t="b">
@@ -5189,15 +5175,15 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>E-Commerce &amp; Retail</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Laptop refresh purchase from Dell India via HDFC Bank</t>
+          <t>Purchase of laptops for IT infrastructure</t>
         </is>
       </c>
       <c r="G112" t="b">
@@ -5231,15 +5217,15 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Software &amp; IT</t>
+          <t>Utilities &amp; Telecom</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Internet bandwidth upgrade payment to Netplus Ilink</t>
+          <t>Internet bandwidth upgrade for business</t>
         </is>
       </c>
       <c r="G113" t="b">
@@ -5277,11 +5263,11 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Autopay payment for TAD Corporate Card statement</t>
+          <t>Autopay credit card repayment for corporate card</t>
         </is>
       </c>
       <c r="G114" t="b">
@@ -5319,11 +5305,11 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Electricity bill payment to MSEDCL via HDFC Bank</t>
+          <t>Electricity bill payment for business</t>
         </is>
       </c>
       <c r="G115" t="b">
@@ -5357,15 +5343,15 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Loan &amp; EMI</t>
+          <t>Interest &amp; Dividends</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Credit interest capitalized likely includes a loan or EMI</t>
+          <t>Capitalised interest for Limited</t>
         </is>
       </c>
       <c r="G116" t="b">
@@ -5403,11 +5389,11 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Office rent payment to Techpark Estates LLP via HDFC Bank</t>
+          <t>Office rent payment, unclear if retail or service</t>
         </is>
       </c>
       <c r="G117" t="b">
@@ -5445,11 +5431,11 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>AWS usage bill payment to Cloudinfra Services via ICICI Bank</t>
+          <t>AWS usage bill for cloud infrastructure</t>
         </is>
       </c>
       <c r="G118" t="b">
@@ -5487,11 +5473,11 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bulk salary payment to 6 employees via HDFC Bank</t>
+          <t>Bulk salary payment for employees</t>
         </is>
       </c>
       <c r="G119" t="b">
@@ -5525,15 +5511,15 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Software &amp; IT</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Retainer and milestone payment to Infozeal Tech Inc</t>
+          <t>Payment for services or products, unclear if retail or service</t>
         </is>
       </c>
       <c r="G120" t="b">
@@ -5571,11 +5557,11 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Recruitment drive payment to LinkedIn India</t>
+          <t>Payment for services or products, unclear if retail or service</t>
         </is>
       </c>
       <c r="G121" t="b">
@@ -5613,11 +5599,11 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Annual infrastructure monitoring plan purchase from Datadog Inc</t>
+          <t>Annual plan for infrastructure monitoring</t>
         </is>
       </c>
       <c r="G122" t="b">
@@ -5659,7 +5645,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>IRCTC train ticket or travel agent payment</t>
+          <t>Business accommodation booking for client presentation</t>
         </is>
       </c>
       <c r="G123" t="b">
@@ -5697,11 +5683,11 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>GST payment for utility or telecom services</t>
+          <t>GST payment for telecom services, unclear if utility or telecom</t>
         </is>
       </c>
       <c r="G124" t="b">
@@ -5735,15 +5721,15 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Software &amp; IT</t>
+          <t>Bank Charges &amp; Fees</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Professional services for software or IT</t>
+          <t>Statutory audit fees, unclear if bank charges or service</t>
         </is>
       </c>
       <c r="G125" t="b">
@@ -5785,7 +5771,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Autopay for credit card dues</t>
+          <t>Autopay credit card repayment for corporate card</t>
         </is>
       </c>
       <c r="G126" t="b">
@@ -5827,7 +5813,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Credit interest capitalized indicates interest and dividend income.</t>
+          <t>Interest capitalised on credit</t>
         </is>
       </c>
       <c r="G127" t="b">
@@ -5865,11 +5851,11 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Office rent payment for commercial property</t>
+          <t>Office rent payment, unclear if retail or service</t>
         </is>
       </c>
       <c r="G128" t="b">
@@ -5911,7 +5897,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Cloud services payment for software or IT</t>
+          <t>AWS usage bill for cloud infrastructure</t>
         </is>
       </c>
       <c r="G129" t="b">
@@ -5949,11 +5935,11 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Salary payment for employees</t>
+          <t>Bulk salary payment for employees with performance bonus</t>
         </is>
       </c>
       <c r="G130" t="b">
@@ -5987,15 +5973,15 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Software &amp; IT</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Professional services for software or IT</t>
+          <t>Payment for services or products, unclear if retail or service</t>
         </is>
       </c>
       <c r="G131" t="b">
@@ -6037,7 +6023,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Purchase of commercial services or products</t>
+          <t>Purchase of annual report package from PR NewsWire India</t>
         </is>
       </c>
       <c r="G132" t="b">
@@ -6071,7 +6057,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Utilities &amp; Telecom</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -6079,7 +6065,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Advance tax payment for utility or telecom services</t>
+          <t>Advance tax payment for Q4 AY 2024-25</t>
         </is>
       </c>
       <c r="G133" t="b">
@@ -6121,7 +6107,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Software subscription for creative services</t>
+          <t>Purchase of Adobe Creative Cloud 10 seats</t>
         </is>
       </c>
       <c r="G134" t="b">
@@ -6163,7 +6149,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Business flight booking for conference</t>
+          <t>Business flight booking for annual conference</t>
         </is>
       </c>
       <c r="G135" t="b">
@@ -6205,7 +6191,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Electricity bill payment for commercial property</t>
+          <t>Electricity bill payment for March 2024</t>
         </is>
       </c>
       <c r="G136" t="b">
@@ -6239,15 +6225,15 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Software &amp; IT</t>
+          <t>Healthcare &amp; Medical</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Professional services for software or IT</t>
+          <t>Possible medical or healthcare-related advisory services</t>
         </is>
       </c>
       <c r="G137" t="b">
@@ -6285,11 +6271,11 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Autopay for credit card dues</t>
+          <t>Credit card autopay for March statement</t>
         </is>
       </c>
       <c r="G138" t="b">
@@ -6323,15 +6309,15 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Loan &amp; EMI</t>
+          <t>Interest &amp; Dividends</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Credit interest capitalized likely includes a loan or EMI</t>
+          <t>Capitalised interest for Limited</t>
         </is>
       </c>
       <c r="G139" t="b">
@@ -6358,7 +6344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6369,156 +6355,156 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>FINANCIAL SUMMARY</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Opening Balance</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>₹1,842,350.00</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Closing Balance</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>₹1,188,320.00</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Total Inflow</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>₹18,838,540.00</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Total Outflow</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>₹19,492,570.00</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Net Cash Flow</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>₹-654,030.00</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Transactions</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>138</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Total Debit</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Total Credit</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Flagged for Review</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1034370</v>
+        <v>220000</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-1034370</v>
+        <v>-220000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E-Commerce &amp; Retail</t>
+          <t>Credit Card Repayment</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>2740000</v>
+        <v>1034370</v>
       </c>
       <c r="D9" t="n">
-        <v>1697900</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-1042100</v>
+        <v>-1034370</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fuel &amp; Auto</t>
+          <t>E-Commerce &amp; Retail</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>370000</v>
+        <v>2859000</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1682860</v>
       </c>
       <c r="E10" t="n">
-        <v>-370000</v>
+        <v>-1176140</v>
       </c>
     </row>
     <row r="11">
@@ -6528,148 +6514,167 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>562000</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2740400</v>
+        <v>3125000</v>
       </c>
       <c r="E11" t="n">
-        <v>2178400</v>
+        <v>3125000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Interest &amp; Dividends</t>
+          <t>Healthcare &amp; Medical</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>265000</v>
+        <v>80000</v>
       </c>
       <c r="D12" t="n">
-        <v>40160</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-224840</v>
+        <v>-80000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Loan &amp; EMI</t>
+          <t>IMPS Transfer</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>26220</v>
+        <v>3726000</v>
       </c>
       <c r="E13" t="n">
-        <v>26220</v>
+        <v>3726000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Interest &amp; Dividends</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>5552000</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>66380</v>
       </c>
       <c r="E14" t="n">
-        <v>-5552000</v>
+        <v>66380</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software &amp; IT</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>6436600</v>
+        <v>6022000</v>
       </c>
       <c r="D15" t="n">
-        <v>14333860</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>7897260</v>
+        <v>-6022000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Travel &amp; Transport</t>
+          <t>Software &amp; IT</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C16" t="n">
-        <v>710100</v>
+        <v>6632600</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>10238300</v>
       </c>
       <c r="E16" t="n">
-        <v>-710100</v>
+        <v>3605700</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Travel &amp; Transport</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" t="n">
+        <v>758100</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-758100</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Utilities &amp; Telecom</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>20</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1822500</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-1822500</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="B18" t="n">
+        <v>21</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1886500</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-1886500</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>── TOTAL ──</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B19" s="7" t="n">
         <v>138</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C19" s="7" t="n">
         <v>19492570</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D19" s="7" t="n">
         <v>18838540</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E19" s="7" t="n">
         <v>-654030</v>
       </c>
     </row>
